--- a/templates/範本-奢華.xlsx
+++ b/templates/範本-奢華.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12285" activeTab="1"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12285"/>
   </bookViews>
   <sheets>
     <sheet name="Overview" sheetId="1" r:id="rId1"/>
@@ -815,18 +815,6 @@
     <xf numFmtId="49" fontId="1" fillId="5" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -863,6 +851,18 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -887,347 +887,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>266700</xdr:colOff>
-      <xdr:row>24</xdr:row>
-      <xdr:rowOff>38100</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="666750" cy="685800"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="image3.png" title="圖片"/>
-        <xdr:cNvPicPr preferRelativeResize="0"/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData fLocksWithSheet="0"/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>95250</xdr:colOff>
-      <xdr:row>24</xdr:row>
-      <xdr:rowOff>38100</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="742950" cy="685800"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="image11.png" title="圖片"/>
-        <xdr:cNvPicPr preferRelativeResize="0"/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2" cstate="print"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData fLocksWithSheet="0"/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>95250</xdr:colOff>
-      <xdr:row>30</xdr:row>
-      <xdr:rowOff>47625</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="742950" cy="742950"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="4" name="image9.png" title="圖片"/>
-        <xdr:cNvPicPr preferRelativeResize="0"/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3" cstate="print"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData fLocksWithSheet="0"/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>30</xdr:row>
-      <xdr:rowOff>47625</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="742950" cy="742950"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="5" name="image1.png" title="圖片"/>
-        <xdr:cNvPicPr preferRelativeResize="0"/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4" cstate="print"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData fLocksWithSheet="0"/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>95250</xdr:colOff>
-      <xdr:row>30</xdr:row>
-      <xdr:rowOff>57150</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="742950" cy="742950"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="6" name="image5.png" title="圖片"/>
-        <xdr:cNvPicPr preferRelativeResize="0"/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5" cstate="print"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData fLocksWithSheet="0"/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>219075</xdr:colOff>
-      <xdr:row>30</xdr:row>
-      <xdr:rowOff>76200</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="666750" cy="685800"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="7" name="image8.png" title="圖片"/>
-        <xdr:cNvPicPr preferRelativeResize="0"/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6" cstate="print"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData fLocksWithSheet="0"/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>161925</xdr:colOff>
-      <xdr:row>30</xdr:row>
-      <xdr:rowOff>57150</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="742950" cy="742950"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="8" name="image6.png" title="圖片"/>
-        <xdr:cNvPicPr preferRelativeResize="0"/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7" cstate="print"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData fLocksWithSheet="0"/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>142875</xdr:colOff>
-      <xdr:row>36</xdr:row>
-      <xdr:rowOff>38100</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="742950" cy="742950"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="9" name="image12.png" title="圖片"/>
-        <xdr:cNvPicPr preferRelativeResize="0"/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8" cstate="print"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData fLocksWithSheet="0"/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>152400</xdr:colOff>
-      <xdr:row>36</xdr:row>
-      <xdr:rowOff>47625</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="742950" cy="742950"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="10" name="image7.png" title="圖片"/>
-        <xdr:cNvPicPr preferRelativeResize="0"/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId9" cstate="print"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData fLocksWithSheet="0"/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>190500</xdr:colOff>
-      <xdr:row>36</xdr:row>
-      <xdr:rowOff>47625</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="742950" cy="742950"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="11" name="image4.png" title="圖片"/>
-        <xdr:cNvPicPr preferRelativeResize="0"/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId10" cstate="print"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData fLocksWithSheet="0"/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>180975</xdr:colOff>
-      <xdr:row>36</xdr:row>
-      <xdr:rowOff>57150</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="666750" cy="685800"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="12" name="image10.png" title="圖片"/>
-        <xdr:cNvPicPr preferRelativeResize="0"/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId11" cstate="print"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData fLocksWithSheet="0"/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>180975</xdr:colOff>
-      <xdr:row>24</xdr:row>
-      <xdr:rowOff>47625</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="666750" cy="685800"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="13" name="image2.png" title="圖片"/>
-        <xdr:cNvPicPr preferRelativeResize="0"/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId12" cstate="print"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData fLocksWithSheet="0"/>
-  </xdr:oneCellAnchor>
-</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1516,10 +1175,10 @@
       </c>
       <c r="H3" s="1"/>
       <c r="I3" s="1"/>
-      <c r="J3" s="47" t="s">
+      <c r="J3" s="59" t="s">
         <v>7</v>
       </c>
-      <c r="K3" s="48"/>
+      <c r="K3" s="60"/>
       <c r="L3" s="1"/>
       <c r="M3" s="1"/>
       <c r="N3" s="1"/>
@@ -1552,23 +1211,23 @@
       </c>
       <c r="H4" s="1"/>
       <c r="I4" s="1"/>
-      <c r="J4" s="49" t="s">
+      <c r="J4" s="61" t="s">
         <v>10</v>
       </c>
-      <c r="K4" s="50"/>
-      <c r="L4" s="50"/>
-      <c r="M4" s="50"/>
-      <c r="N4" s="50"/>
-      <c r="O4" s="50"/>
-      <c r="P4" s="50"/>
-      <c r="Q4" s="50"/>
-      <c r="R4" s="50"/>
-      <c r="S4" s="50"/>
-      <c r="T4" s="50"/>
-      <c r="U4" s="50"/>
-      <c r="V4" s="50"/>
-      <c r="W4" s="50"/>
-      <c r="X4" s="50"/>
+      <c r="K4" s="62"/>
+      <c r="L4" s="62"/>
+      <c r="M4" s="62"/>
+      <c r="N4" s="62"/>
+      <c r="O4" s="62"/>
+      <c r="P4" s="62"/>
+      <c r="Q4" s="62"/>
+      <c r="R4" s="62"/>
+      <c r="S4" s="62"/>
+      <c r="T4" s="62"/>
+      <c r="U4" s="62"/>
+      <c r="V4" s="62"/>
+      <c r="W4" s="62"/>
+      <c r="X4" s="62"/>
       <c r="Y4" s="1"/>
       <c r="Z4" s="1"/>
     </row>
@@ -1584,21 +1243,21 @@
       <c r="G5" s="3"/>
       <c r="H5" s="1"/>
       <c r="I5" s="1"/>
-      <c r="J5" s="50"/>
-      <c r="K5" s="50"/>
-      <c r="L5" s="50"/>
-      <c r="M5" s="50"/>
-      <c r="N5" s="50"/>
-      <c r="O5" s="50"/>
-      <c r="P5" s="50"/>
-      <c r="Q5" s="50"/>
-      <c r="R5" s="50"/>
-      <c r="S5" s="50"/>
-      <c r="T5" s="50"/>
-      <c r="U5" s="50"/>
-      <c r="V5" s="50"/>
-      <c r="W5" s="50"/>
-      <c r="X5" s="50"/>
+      <c r="J5" s="62"/>
+      <c r="K5" s="62"/>
+      <c r="L5" s="62"/>
+      <c r="M5" s="62"/>
+      <c r="N5" s="62"/>
+      <c r="O5" s="62"/>
+      <c r="P5" s="62"/>
+      <c r="Q5" s="62"/>
+      <c r="R5" s="62"/>
+      <c r="S5" s="62"/>
+      <c r="T5" s="62"/>
+      <c r="U5" s="62"/>
+      <c r="V5" s="62"/>
+      <c r="W5" s="62"/>
+      <c r="X5" s="62"/>
       <c r="Y5" s="1"/>
       <c r="Z5" s="1"/>
     </row>
@@ -1624,21 +1283,21 @@
       </c>
       <c r="H6" s="1"/>
       <c r="I6" s="1"/>
-      <c r="J6" s="50"/>
-      <c r="K6" s="50"/>
-      <c r="L6" s="50"/>
-      <c r="M6" s="50"/>
-      <c r="N6" s="50"/>
-      <c r="O6" s="50"/>
-      <c r="P6" s="50"/>
-      <c r="Q6" s="50"/>
-      <c r="R6" s="50"/>
-      <c r="S6" s="50"/>
-      <c r="T6" s="50"/>
-      <c r="U6" s="50"/>
-      <c r="V6" s="50"/>
-      <c r="W6" s="50"/>
-      <c r="X6" s="50"/>
+      <c r="J6" s="62"/>
+      <c r="K6" s="62"/>
+      <c r="L6" s="62"/>
+      <c r="M6" s="62"/>
+      <c r="N6" s="62"/>
+      <c r="O6" s="62"/>
+      <c r="P6" s="62"/>
+      <c r="Q6" s="62"/>
+      <c r="R6" s="62"/>
+      <c r="S6" s="62"/>
+      <c r="T6" s="62"/>
+      <c r="U6" s="62"/>
+      <c r="V6" s="62"/>
+      <c r="W6" s="62"/>
+      <c r="X6" s="62"/>
       <c r="Y6" s="1"/>
       <c r="Z6" s="1"/>
     </row>
@@ -1658,21 +1317,21 @@
       </c>
       <c r="H7" s="1"/>
       <c r="I7" s="1"/>
-      <c r="J7" s="50"/>
-      <c r="K7" s="50"/>
-      <c r="L7" s="50"/>
-      <c r="M7" s="50"/>
-      <c r="N7" s="50"/>
-      <c r="O7" s="50"/>
-      <c r="P7" s="50"/>
-      <c r="Q7" s="50"/>
-      <c r="R7" s="50"/>
-      <c r="S7" s="50"/>
-      <c r="T7" s="50"/>
-      <c r="U7" s="50"/>
-      <c r="V7" s="50"/>
-      <c r="W7" s="50"/>
-      <c r="X7" s="50"/>
+      <c r="J7" s="62"/>
+      <c r="K7" s="62"/>
+      <c r="L7" s="62"/>
+      <c r="M7" s="62"/>
+      <c r="N7" s="62"/>
+      <c r="O7" s="62"/>
+      <c r="P7" s="62"/>
+      <c r="Q7" s="62"/>
+      <c r="R7" s="62"/>
+      <c r="S7" s="62"/>
+      <c r="T7" s="62"/>
+      <c r="U7" s="62"/>
+      <c r="V7" s="62"/>
+      <c r="W7" s="62"/>
+      <c r="X7" s="62"/>
       <c r="Y7" s="1"/>
       <c r="Z7" s="1"/>
     </row>
@@ -1688,21 +1347,21 @@
       <c r="G8" s="1"/>
       <c r="H8" s="1"/>
       <c r="I8" s="1"/>
-      <c r="J8" s="50"/>
-      <c r="K8" s="50"/>
-      <c r="L8" s="50"/>
-      <c r="M8" s="50"/>
-      <c r="N8" s="50"/>
-      <c r="O8" s="50"/>
-      <c r="P8" s="50"/>
-      <c r="Q8" s="50"/>
-      <c r="R8" s="50"/>
-      <c r="S8" s="50"/>
-      <c r="T8" s="50"/>
-      <c r="U8" s="50"/>
-      <c r="V8" s="50"/>
-      <c r="W8" s="50"/>
-      <c r="X8" s="50"/>
+      <c r="J8" s="62"/>
+      <c r="K8" s="62"/>
+      <c r="L8" s="62"/>
+      <c r="M8" s="62"/>
+      <c r="N8" s="62"/>
+      <c r="O8" s="62"/>
+      <c r="P8" s="62"/>
+      <c r="Q8" s="62"/>
+      <c r="R8" s="62"/>
+      <c r="S8" s="62"/>
+      <c r="T8" s="62"/>
+      <c r="U8" s="62"/>
+      <c r="V8" s="62"/>
+      <c r="W8" s="62"/>
+      <c r="X8" s="62"/>
       <c r="Y8" s="1"/>
       <c r="Z8" s="1"/>
     </row>
@@ -1730,21 +1389,21 @@
         <v>13</v>
       </c>
       <c r="I9" s="1"/>
-      <c r="J9" s="50"/>
-      <c r="K9" s="50"/>
-      <c r="L9" s="50"/>
-      <c r="M9" s="50"/>
-      <c r="N9" s="50"/>
-      <c r="O9" s="50"/>
-      <c r="P9" s="50"/>
-      <c r="Q9" s="50"/>
-      <c r="R9" s="50"/>
-      <c r="S9" s="50"/>
-      <c r="T9" s="50"/>
-      <c r="U9" s="50"/>
-      <c r="V9" s="50"/>
-      <c r="W9" s="50"/>
-      <c r="X9" s="50"/>
+      <c r="J9" s="62"/>
+      <c r="K9" s="62"/>
+      <c r="L9" s="62"/>
+      <c r="M9" s="62"/>
+      <c r="N9" s="62"/>
+      <c r="O9" s="62"/>
+      <c r="P9" s="62"/>
+      <c r="Q9" s="62"/>
+      <c r="R9" s="62"/>
+      <c r="S9" s="62"/>
+      <c r="T9" s="62"/>
+      <c r="U9" s="62"/>
+      <c r="V9" s="62"/>
+      <c r="W9" s="62"/>
+      <c r="X9" s="62"/>
       <c r="Y9" s="1"/>
       <c r="Z9" s="1"/>
     </row>
@@ -1766,21 +1425,21 @@
         <v>14</v>
       </c>
       <c r="I10" s="1"/>
-      <c r="J10" s="50"/>
-      <c r="K10" s="50"/>
-      <c r="L10" s="50"/>
-      <c r="M10" s="50"/>
-      <c r="N10" s="50"/>
-      <c r="O10" s="50"/>
-      <c r="P10" s="50"/>
-      <c r="Q10" s="50"/>
-      <c r="R10" s="50"/>
-      <c r="S10" s="50"/>
-      <c r="T10" s="50"/>
-      <c r="U10" s="50"/>
-      <c r="V10" s="50"/>
-      <c r="W10" s="50"/>
-      <c r="X10" s="50"/>
+      <c r="J10" s="62"/>
+      <c r="K10" s="62"/>
+      <c r="L10" s="62"/>
+      <c r="M10" s="62"/>
+      <c r="N10" s="62"/>
+      <c r="O10" s="62"/>
+      <c r="P10" s="62"/>
+      <c r="Q10" s="62"/>
+      <c r="R10" s="62"/>
+      <c r="S10" s="62"/>
+      <c r="T10" s="62"/>
+      <c r="U10" s="62"/>
+      <c r="V10" s="62"/>
+      <c r="W10" s="62"/>
+      <c r="X10" s="62"/>
       <c r="Y10" s="1"/>
       <c r="Z10" s="1"/>
     </row>
@@ -1796,21 +1455,21 @@
       <c r="G11" s="1"/>
       <c r="H11" s="1"/>
       <c r="I11" s="1"/>
-      <c r="J11" s="50"/>
-      <c r="K11" s="50"/>
-      <c r="L11" s="50"/>
-      <c r="M11" s="50"/>
-      <c r="N11" s="50"/>
-      <c r="O11" s="50"/>
-      <c r="P11" s="50"/>
-      <c r="Q11" s="50"/>
-      <c r="R11" s="50"/>
-      <c r="S11" s="50"/>
-      <c r="T11" s="50"/>
-      <c r="U11" s="50"/>
-      <c r="V11" s="50"/>
-      <c r="W11" s="50"/>
-      <c r="X11" s="50"/>
+      <c r="J11" s="62"/>
+      <c r="K11" s="62"/>
+      <c r="L11" s="62"/>
+      <c r="M11" s="62"/>
+      <c r="N11" s="62"/>
+      <c r="O11" s="62"/>
+      <c r="P11" s="62"/>
+      <c r="Q11" s="62"/>
+      <c r="R11" s="62"/>
+      <c r="S11" s="62"/>
+      <c r="T11" s="62"/>
+      <c r="U11" s="62"/>
+      <c r="V11" s="62"/>
+      <c r="W11" s="62"/>
+      <c r="X11" s="62"/>
       <c r="Y11" s="1"/>
       <c r="Z11" s="1"/>
     </row>
@@ -1838,21 +1497,21 @@
         <v>13</v>
       </c>
       <c r="I12" s="1"/>
-      <c r="J12" s="50"/>
-      <c r="K12" s="50"/>
-      <c r="L12" s="50"/>
-      <c r="M12" s="50"/>
-      <c r="N12" s="50"/>
-      <c r="O12" s="50"/>
-      <c r="P12" s="50"/>
-      <c r="Q12" s="50"/>
-      <c r="R12" s="50"/>
-      <c r="S12" s="50"/>
-      <c r="T12" s="50"/>
-      <c r="U12" s="50"/>
-      <c r="V12" s="50"/>
-      <c r="W12" s="50"/>
-      <c r="X12" s="50"/>
+      <c r="J12" s="62"/>
+      <c r="K12" s="62"/>
+      <c r="L12" s="62"/>
+      <c r="M12" s="62"/>
+      <c r="N12" s="62"/>
+      <c r="O12" s="62"/>
+      <c r="P12" s="62"/>
+      <c r="Q12" s="62"/>
+      <c r="R12" s="62"/>
+      <c r="S12" s="62"/>
+      <c r="T12" s="62"/>
+      <c r="U12" s="62"/>
+      <c r="V12" s="62"/>
+      <c r="W12" s="62"/>
+      <c r="X12" s="62"/>
       <c r="Y12" s="1"/>
       <c r="Z12" s="1"/>
     </row>
@@ -1874,21 +1533,21 @@
         <v>16</v>
       </c>
       <c r="I13" s="1"/>
-      <c r="J13" s="50"/>
-      <c r="K13" s="50"/>
-      <c r="L13" s="50"/>
-      <c r="M13" s="50"/>
-      <c r="N13" s="50"/>
-      <c r="O13" s="50"/>
-      <c r="P13" s="50"/>
-      <c r="Q13" s="50"/>
-      <c r="R13" s="50"/>
-      <c r="S13" s="50"/>
-      <c r="T13" s="50"/>
-      <c r="U13" s="50"/>
-      <c r="V13" s="50"/>
-      <c r="W13" s="50"/>
-      <c r="X13" s="50"/>
+      <c r="J13" s="62"/>
+      <c r="K13" s="62"/>
+      <c r="L13" s="62"/>
+      <c r="M13" s="62"/>
+      <c r="N13" s="62"/>
+      <c r="O13" s="62"/>
+      <c r="P13" s="62"/>
+      <c r="Q13" s="62"/>
+      <c r="R13" s="62"/>
+      <c r="S13" s="62"/>
+      <c r="T13" s="62"/>
+      <c r="U13" s="62"/>
+      <c r="V13" s="62"/>
+      <c r="W13" s="62"/>
+      <c r="X13" s="62"/>
       <c r="Y13" s="1"/>
       <c r="Z13" s="1"/>
     </row>
@@ -1904,21 +1563,21 @@
       <c r="G14" s="1"/>
       <c r="H14" s="1"/>
       <c r="I14" s="1"/>
-      <c r="J14" s="50"/>
-      <c r="K14" s="50"/>
-      <c r="L14" s="50"/>
-      <c r="M14" s="50"/>
-      <c r="N14" s="50"/>
-      <c r="O14" s="50"/>
-      <c r="P14" s="50"/>
-      <c r="Q14" s="50"/>
-      <c r="R14" s="50"/>
-      <c r="S14" s="50"/>
-      <c r="T14" s="50"/>
-      <c r="U14" s="50"/>
-      <c r="V14" s="50"/>
-      <c r="W14" s="50"/>
-      <c r="X14" s="50"/>
+      <c r="J14" s="62"/>
+      <c r="K14" s="62"/>
+      <c r="L14" s="62"/>
+      <c r="M14" s="62"/>
+      <c r="N14" s="62"/>
+      <c r="O14" s="62"/>
+      <c r="P14" s="62"/>
+      <c r="Q14" s="62"/>
+      <c r="R14" s="62"/>
+      <c r="S14" s="62"/>
+      <c r="T14" s="62"/>
+      <c r="U14" s="62"/>
+      <c r="V14" s="62"/>
+      <c r="W14" s="62"/>
+      <c r="X14" s="62"/>
       <c r="Y14" s="1"/>
       <c r="Z14" s="1"/>
     </row>
@@ -1946,21 +1605,21 @@
         <v>13</v>
       </c>
       <c r="I15" s="1"/>
-      <c r="J15" s="50"/>
-      <c r="K15" s="50"/>
-      <c r="L15" s="50"/>
-      <c r="M15" s="50"/>
-      <c r="N15" s="50"/>
-      <c r="O15" s="50"/>
-      <c r="P15" s="50"/>
-      <c r="Q15" s="50"/>
-      <c r="R15" s="50"/>
-      <c r="S15" s="50"/>
-      <c r="T15" s="50"/>
-      <c r="U15" s="50"/>
-      <c r="V15" s="50"/>
-      <c r="W15" s="50"/>
-      <c r="X15" s="50"/>
+      <c r="J15" s="62"/>
+      <c r="K15" s="62"/>
+      <c r="L15" s="62"/>
+      <c r="M15" s="62"/>
+      <c r="N15" s="62"/>
+      <c r="O15" s="62"/>
+      <c r="P15" s="62"/>
+      <c r="Q15" s="62"/>
+      <c r="R15" s="62"/>
+      <c r="S15" s="62"/>
+      <c r="T15" s="62"/>
+      <c r="U15" s="62"/>
+      <c r="V15" s="62"/>
+      <c r="W15" s="62"/>
+      <c r="X15" s="62"/>
       <c r="Y15" s="1"/>
       <c r="Z15" s="1"/>
     </row>
@@ -1982,21 +1641,21 @@
         <v>18</v>
       </c>
       <c r="I16" s="1"/>
-      <c r="J16" s="50"/>
-      <c r="K16" s="50"/>
-      <c r="L16" s="50"/>
-      <c r="M16" s="50"/>
-      <c r="N16" s="50"/>
-      <c r="O16" s="50"/>
-      <c r="P16" s="50"/>
-      <c r="Q16" s="50"/>
-      <c r="R16" s="50"/>
-      <c r="S16" s="50"/>
-      <c r="T16" s="50"/>
-      <c r="U16" s="50"/>
-      <c r="V16" s="50"/>
-      <c r="W16" s="50"/>
-      <c r="X16" s="50"/>
+      <c r="J16" s="62"/>
+      <c r="K16" s="62"/>
+      <c r="L16" s="62"/>
+      <c r="M16" s="62"/>
+      <c r="N16" s="62"/>
+      <c r="O16" s="62"/>
+      <c r="P16" s="62"/>
+      <c r="Q16" s="62"/>
+      <c r="R16" s="62"/>
+      <c r="S16" s="62"/>
+      <c r="T16" s="62"/>
+      <c r="U16" s="62"/>
+      <c r="V16" s="62"/>
+      <c r="W16" s="62"/>
+      <c r="X16" s="62"/>
       <c r="Y16" s="1"/>
       <c r="Z16" s="1"/>
     </row>
@@ -2010,21 +1669,21 @@
       <c r="G17" s="1"/>
       <c r="H17" s="1"/>
       <c r="I17" s="1"/>
-      <c r="J17" s="50"/>
-      <c r="K17" s="50"/>
-      <c r="L17" s="50"/>
-      <c r="M17" s="50"/>
-      <c r="N17" s="50"/>
-      <c r="O17" s="50"/>
-      <c r="P17" s="50"/>
-      <c r="Q17" s="50"/>
-      <c r="R17" s="50"/>
-      <c r="S17" s="50"/>
-      <c r="T17" s="50"/>
-      <c r="U17" s="50"/>
-      <c r="V17" s="50"/>
-      <c r="W17" s="50"/>
-      <c r="X17" s="50"/>
+      <c r="J17" s="62"/>
+      <c r="K17" s="62"/>
+      <c r="L17" s="62"/>
+      <c r="M17" s="62"/>
+      <c r="N17" s="62"/>
+      <c r="O17" s="62"/>
+      <c r="P17" s="62"/>
+      <c r="Q17" s="62"/>
+      <c r="R17" s="62"/>
+      <c r="S17" s="62"/>
+      <c r="T17" s="62"/>
+      <c r="U17" s="62"/>
+      <c r="V17" s="62"/>
+      <c r="W17" s="62"/>
+      <c r="X17" s="62"/>
       <c r="Y17" s="1"/>
       <c r="Z17" s="1"/>
     </row>
@@ -2050,21 +1709,21 @@
       </c>
       <c r="H18" s="1"/>
       <c r="I18" s="1"/>
-      <c r="J18" s="50"/>
-      <c r="K18" s="50"/>
-      <c r="L18" s="50"/>
-      <c r="M18" s="50"/>
-      <c r="N18" s="50"/>
-      <c r="O18" s="50"/>
-      <c r="P18" s="50"/>
-      <c r="Q18" s="50"/>
-      <c r="R18" s="50"/>
-      <c r="S18" s="50"/>
-      <c r="T18" s="50"/>
-      <c r="U18" s="50"/>
-      <c r="V18" s="50"/>
-      <c r="W18" s="50"/>
-      <c r="X18" s="50"/>
+      <c r="J18" s="62"/>
+      <c r="K18" s="62"/>
+      <c r="L18" s="62"/>
+      <c r="M18" s="62"/>
+      <c r="N18" s="62"/>
+      <c r="O18" s="62"/>
+      <c r="P18" s="62"/>
+      <c r="Q18" s="62"/>
+      <c r="R18" s="62"/>
+      <c r="S18" s="62"/>
+      <c r="T18" s="62"/>
+      <c r="U18" s="62"/>
+      <c r="V18" s="62"/>
+      <c r="W18" s="62"/>
+      <c r="X18" s="62"/>
       <c r="Y18" s="1"/>
       <c r="Z18" s="1"/>
     </row>
@@ -2090,21 +1749,21 @@
       </c>
       <c r="H19" s="1"/>
       <c r="I19" s="1"/>
-      <c r="J19" s="50"/>
-      <c r="K19" s="50"/>
-      <c r="L19" s="50"/>
-      <c r="M19" s="50"/>
-      <c r="N19" s="50"/>
-      <c r="O19" s="50"/>
-      <c r="P19" s="50"/>
-      <c r="Q19" s="50"/>
-      <c r="R19" s="50"/>
-      <c r="S19" s="50"/>
-      <c r="T19" s="50"/>
-      <c r="U19" s="50"/>
-      <c r="V19" s="50"/>
-      <c r="W19" s="50"/>
-      <c r="X19" s="50"/>
+      <c r="J19" s="62"/>
+      <c r="K19" s="62"/>
+      <c r="L19" s="62"/>
+      <c r="M19" s="62"/>
+      <c r="N19" s="62"/>
+      <c r="O19" s="62"/>
+      <c r="P19" s="62"/>
+      <c r="Q19" s="62"/>
+      <c r="R19" s="62"/>
+      <c r="S19" s="62"/>
+      <c r="T19" s="62"/>
+      <c r="U19" s="62"/>
+      <c r="V19" s="62"/>
+      <c r="W19" s="62"/>
+      <c r="X19" s="62"/>
       <c r="Y19" s="1"/>
       <c r="Z19" s="1"/>
     </row>
@@ -2118,21 +1777,21 @@
       <c r="G20" s="22"/>
       <c r="H20" s="1"/>
       <c r="I20" s="1"/>
-      <c r="J20" s="50"/>
-      <c r="K20" s="50"/>
-      <c r="L20" s="50"/>
-      <c r="M20" s="50"/>
-      <c r="N20" s="50"/>
-      <c r="O20" s="50"/>
-      <c r="P20" s="50"/>
-      <c r="Q20" s="50"/>
-      <c r="R20" s="50"/>
-      <c r="S20" s="50"/>
-      <c r="T20" s="50"/>
-      <c r="U20" s="50"/>
-      <c r="V20" s="50"/>
-      <c r="W20" s="50"/>
-      <c r="X20" s="50"/>
+      <c r="J20" s="62"/>
+      <c r="K20" s="62"/>
+      <c r="L20" s="62"/>
+      <c r="M20" s="62"/>
+      <c r="N20" s="62"/>
+      <c r="O20" s="62"/>
+      <c r="P20" s="62"/>
+      <c r="Q20" s="62"/>
+      <c r="R20" s="62"/>
+      <c r="S20" s="62"/>
+      <c r="T20" s="62"/>
+      <c r="U20" s="62"/>
+      <c r="V20" s="62"/>
+      <c r="W20" s="62"/>
+      <c r="X20" s="62"/>
       <c r="Y20" s="1"/>
       <c r="Z20" s="1"/>
     </row>
@@ -2150,21 +1809,21 @@
       <c r="G21" s="22"/>
       <c r="H21" s="1"/>
       <c r="I21" s="1"/>
-      <c r="J21" s="50"/>
-      <c r="K21" s="50"/>
-      <c r="L21" s="50"/>
-      <c r="M21" s="50"/>
-      <c r="N21" s="50"/>
-      <c r="O21" s="50"/>
-      <c r="P21" s="50"/>
-      <c r="Q21" s="50"/>
-      <c r="R21" s="50"/>
-      <c r="S21" s="50"/>
-      <c r="T21" s="50"/>
-      <c r="U21" s="50"/>
-      <c r="V21" s="50"/>
-      <c r="W21" s="50"/>
-      <c r="X21" s="50"/>
+      <c r="J21" s="62"/>
+      <c r="K21" s="62"/>
+      <c r="L21" s="62"/>
+      <c r="M21" s="62"/>
+      <c r="N21" s="62"/>
+      <c r="O21" s="62"/>
+      <c r="P21" s="62"/>
+      <c r="Q21" s="62"/>
+      <c r="R21" s="62"/>
+      <c r="S21" s="62"/>
+      <c r="T21" s="62"/>
+      <c r="U21" s="62"/>
+      <c r="V21" s="62"/>
+      <c r="W21" s="62"/>
+      <c r="X21" s="62"/>
       <c r="Y21" s="1"/>
       <c r="Z21" s="1"/>
     </row>
@@ -2179,21 +1838,21 @@
       <c r="F22" s="1"/>
       <c r="G22" s="22"/>
       <c r="I22" s="1"/>
-      <c r="J22" s="50"/>
-      <c r="K22" s="50"/>
-      <c r="L22" s="50"/>
-      <c r="M22" s="50"/>
-      <c r="N22" s="50"/>
-      <c r="O22" s="50"/>
-      <c r="P22" s="50"/>
-      <c r="Q22" s="50"/>
-      <c r="R22" s="50"/>
-      <c r="S22" s="50"/>
-      <c r="T22" s="50"/>
-      <c r="U22" s="50"/>
-      <c r="V22" s="50"/>
-      <c r="W22" s="50"/>
-      <c r="X22" s="50"/>
+      <c r="J22" s="62"/>
+      <c r="K22" s="62"/>
+      <c r="L22" s="62"/>
+      <c r="M22" s="62"/>
+      <c r="N22" s="62"/>
+      <c r="O22" s="62"/>
+      <c r="P22" s="62"/>
+      <c r="Q22" s="62"/>
+      <c r="R22" s="62"/>
+      <c r="S22" s="62"/>
+      <c r="T22" s="62"/>
+      <c r="U22" s="62"/>
+      <c r="V22" s="62"/>
+      <c r="W22" s="62"/>
+      <c r="X22" s="62"/>
       <c r="Y22" s="1"/>
       <c r="Z22" s="1"/>
     </row>
@@ -2213,21 +1872,21 @@
       <c r="G23" s="36"/>
       <c r="H23" s="36"/>
       <c r="I23" s="1"/>
-      <c r="J23" s="50"/>
-      <c r="K23" s="50"/>
-      <c r="L23" s="50"/>
-      <c r="M23" s="50"/>
-      <c r="N23" s="50"/>
-      <c r="O23" s="50"/>
-      <c r="P23" s="50"/>
-      <c r="Q23" s="50"/>
-      <c r="R23" s="50"/>
-      <c r="S23" s="50"/>
-      <c r="T23" s="50"/>
-      <c r="U23" s="50"/>
-      <c r="V23" s="50"/>
-      <c r="W23" s="50"/>
-      <c r="X23" s="50"/>
+      <c r="J23" s="62"/>
+      <c r="K23" s="62"/>
+      <c r="L23" s="62"/>
+      <c r="M23" s="62"/>
+      <c r="N23" s="62"/>
+      <c r="O23" s="62"/>
+      <c r="P23" s="62"/>
+      <c r="Q23" s="62"/>
+      <c r="R23" s="62"/>
+      <c r="S23" s="62"/>
+      <c r="T23" s="62"/>
+      <c r="U23" s="62"/>
+      <c r="V23" s="62"/>
+      <c r="W23" s="62"/>
+      <c r="X23" s="62"/>
       <c r="Y23" s="1"/>
       <c r="Z23" s="1"/>
     </row>
@@ -2249,21 +1908,21 @@
       <c r="G24" s="39"/>
       <c r="H24" s="39"/>
       <c r="I24" s="1"/>
-      <c r="J24" s="50"/>
-      <c r="K24" s="50"/>
-      <c r="L24" s="50"/>
-      <c r="M24" s="50"/>
-      <c r="N24" s="50"/>
-      <c r="O24" s="50"/>
-      <c r="P24" s="50"/>
-      <c r="Q24" s="50"/>
-      <c r="R24" s="50"/>
-      <c r="S24" s="50"/>
-      <c r="T24" s="50"/>
-      <c r="U24" s="50"/>
-      <c r="V24" s="50"/>
-      <c r="W24" s="50"/>
-      <c r="X24" s="50"/>
+      <c r="J24" s="62"/>
+      <c r="K24" s="62"/>
+      <c r="L24" s="62"/>
+      <c r="M24" s="62"/>
+      <c r="N24" s="62"/>
+      <c r="O24" s="62"/>
+      <c r="P24" s="62"/>
+      <c r="Q24" s="62"/>
+      <c r="R24" s="62"/>
+      <c r="S24" s="62"/>
+      <c r="T24" s="62"/>
+      <c r="U24" s="62"/>
+      <c r="V24" s="62"/>
+      <c r="W24" s="62"/>
+      <c r="X24" s="62"/>
       <c r="Y24" s="1"/>
       <c r="Z24" s="1"/>
     </row>
@@ -2279,21 +1938,21 @@
       <c r="G25" s="39"/>
       <c r="H25" s="39"/>
       <c r="I25" s="1"/>
-      <c r="J25" s="50"/>
-      <c r="K25" s="50"/>
-      <c r="L25" s="50"/>
-      <c r="M25" s="50"/>
-      <c r="N25" s="50"/>
-      <c r="O25" s="50"/>
-      <c r="P25" s="50"/>
-      <c r="Q25" s="50"/>
-      <c r="R25" s="50"/>
-      <c r="S25" s="50"/>
-      <c r="T25" s="50"/>
-      <c r="U25" s="50"/>
-      <c r="V25" s="50"/>
-      <c r="W25" s="50"/>
-      <c r="X25" s="50"/>
+      <c r="J25" s="62"/>
+      <c r="K25" s="62"/>
+      <c r="L25" s="62"/>
+      <c r="M25" s="62"/>
+      <c r="N25" s="62"/>
+      <c r="O25" s="62"/>
+      <c r="P25" s="62"/>
+      <c r="Q25" s="62"/>
+      <c r="R25" s="62"/>
+      <c r="S25" s="62"/>
+      <c r="T25" s="62"/>
+      <c r="U25" s="62"/>
+      <c r="V25" s="62"/>
+      <c r="W25" s="62"/>
+      <c r="X25" s="62"/>
       <c r="Y25" s="1"/>
       <c r="Z25" s="1"/>
     </row>
@@ -2315,21 +1974,21 @@
       <c r="G26" s="39"/>
       <c r="H26" s="39"/>
       <c r="I26" s="1"/>
-      <c r="J26" s="50"/>
-      <c r="K26" s="50"/>
-      <c r="L26" s="50"/>
-      <c r="M26" s="50"/>
-      <c r="N26" s="50"/>
-      <c r="O26" s="50"/>
-      <c r="P26" s="50"/>
-      <c r="Q26" s="50"/>
-      <c r="R26" s="50"/>
-      <c r="S26" s="50"/>
-      <c r="T26" s="50"/>
-      <c r="U26" s="50"/>
-      <c r="V26" s="50"/>
-      <c r="W26" s="50"/>
-      <c r="X26" s="50"/>
+      <c r="J26" s="62"/>
+      <c r="K26" s="62"/>
+      <c r="L26" s="62"/>
+      <c r="M26" s="62"/>
+      <c r="N26" s="62"/>
+      <c r="O26" s="62"/>
+      <c r="P26" s="62"/>
+      <c r="Q26" s="62"/>
+      <c r="R26" s="62"/>
+      <c r="S26" s="62"/>
+      <c r="T26" s="62"/>
+      <c r="U26" s="62"/>
+      <c r="V26" s="62"/>
+      <c r="W26" s="62"/>
+      <c r="X26" s="62"/>
       <c r="Y26" s="1"/>
       <c r="Z26" s="1"/>
     </row>
@@ -2351,21 +2010,21 @@
       <c r="G27" s="39"/>
       <c r="H27" s="39"/>
       <c r="I27" s="1"/>
-      <c r="J27" s="50"/>
-      <c r="K27" s="50"/>
-      <c r="L27" s="50"/>
-      <c r="M27" s="50"/>
-      <c r="N27" s="50"/>
-      <c r="O27" s="50"/>
-      <c r="P27" s="50"/>
-      <c r="Q27" s="50"/>
-      <c r="R27" s="50"/>
-      <c r="S27" s="50"/>
-      <c r="T27" s="50"/>
-      <c r="U27" s="50"/>
-      <c r="V27" s="50"/>
-      <c r="W27" s="50"/>
-      <c r="X27" s="50"/>
+      <c r="J27" s="62"/>
+      <c r="K27" s="62"/>
+      <c r="L27" s="62"/>
+      <c r="M27" s="62"/>
+      <c r="N27" s="62"/>
+      <c r="O27" s="62"/>
+      <c r="P27" s="62"/>
+      <c r="Q27" s="62"/>
+      <c r="R27" s="62"/>
+      <c r="S27" s="62"/>
+      <c r="T27" s="62"/>
+      <c r="U27" s="62"/>
+      <c r="V27" s="62"/>
+      <c r="W27" s="62"/>
+      <c r="X27" s="62"/>
       <c r="Y27" s="1"/>
       <c r="Z27" s="1"/>
     </row>
@@ -2387,21 +2046,21 @@
       <c r="G28" s="39"/>
       <c r="H28" s="39"/>
       <c r="I28" s="1"/>
-      <c r="J28" s="50"/>
-      <c r="K28" s="50"/>
-      <c r="L28" s="50"/>
-      <c r="M28" s="50"/>
-      <c r="N28" s="50"/>
-      <c r="O28" s="50"/>
-      <c r="P28" s="50"/>
-      <c r="Q28" s="50"/>
-      <c r="R28" s="50"/>
-      <c r="S28" s="50"/>
-      <c r="T28" s="50"/>
-      <c r="U28" s="50"/>
-      <c r="V28" s="50"/>
-      <c r="W28" s="50"/>
-      <c r="X28" s="50"/>
+      <c r="J28" s="62"/>
+      <c r="K28" s="62"/>
+      <c r="L28" s="62"/>
+      <c r="M28" s="62"/>
+      <c r="N28" s="62"/>
+      <c r="O28" s="62"/>
+      <c r="P28" s="62"/>
+      <c r="Q28" s="62"/>
+      <c r="R28" s="62"/>
+      <c r="S28" s="62"/>
+      <c r="T28" s="62"/>
+      <c r="U28" s="62"/>
+      <c r="V28" s="62"/>
+      <c r="W28" s="62"/>
+      <c r="X28" s="62"/>
       <c r="Y28" s="1"/>
       <c r="Z28" s="1"/>
     </row>
@@ -2427,21 +2086,21 @@
         <v>38</v>
       </c>
       <c r="I29" s="1"/>
-      <c r="J29" s="50"/>
-      <c r="K29" s="50"/>
-      <c r="L29" s="50"/>
-      <c r="M29" s="50"/>
-      <c r="N29" s="50"/>
-      <c r="O29" s="50"/>
-      <c r="P29" s="50"/>
-      <c r="Q29" s="50"/>
-      <c r="R29" s="50"/>
-      <c r="S29" s="50"/>
-      <c r="T29" s="50"/>
-      <c r="U29" s="50"/>
-      <c r="V29" s="50"/>
-      <c r="W29" s="50"/>
-      <c r="X29" s="50"/>
+      <c r="J29" s="62"/>
+      <c r="K29" s="62"/>
+      <c r="L29" s="62"/>
+      <c r="M29" s="62"/>
+      <c r="N29" s="62"/>
+      <c r="O29" s="62"/>
+      <c r="P29" s="62"/>
+      <c r="Q29" s="62"/>
+      <c r="R29" s="62"/>
+      <c r="S29" s="62"/>
+      <c r="T29" s="62"/>
+      <c r="U29" s="62"/>
+      <c r="V29" s="62"/>
+      <c r="W29" s="62"/>
+      <c r="X29" s="62"/>
       <c r="Y29" s="1"/>
       <c r="Z29" s="1"/>
     </row>
@@ -2467,21 +2126,21 @@
       </c>
       <c r="H30" s="44"/>
       <c r="I30" s="1"/>
-      <c r="J30" s="50"/>
-      <c r="K30" s="50"/>
-      <c r="L30" s="50"/>
-      <c r="M30" s="50"/>
-      <c r="N30" s="50"/>
-      <c r="O30" s="50"/>
-      <c r="P30" s="50"/>
-      <c r="Q30" s="50"/>
-      <c r="R30" s="50"/>
-      <c r="S30" s="50"/>
-      <c r="T30" s="50"/>
-      <c r="U30" s="50"/>
-      <c r="V30" s="50"/>
-      <c r="W30" s="50"/>
-      <c r="X30" s="50"/>
+      <c r="J30" s="62"/>
+      <c r="K30" s="62"/>
+      <c r="L30" s="62"/>
+      <c r="M30" s="62"/>
+      <c r="N30" s="62"/>
+      <c r="O30" s="62"/>
+      <c r="P30" s="62"/>
+      <c r="Q30" s="62"/>
+      <c r="R30" s="62"/>
+      <c r="S30" s="62"/>
+      <c r="T30" s="62"/>
+      <c r="U30" s="62"/>
+      <c r="V30" s="62"/>
+      <c r="W30" s="62"/>
+      <c r="X30" s="62"/>
       <c r="Y30" s="1"/>
       <c r="Z30" s="1"/>
     </row>
@@ -2497,21 +2156,21 @@
       <c r="G31" s="45"/>
       <c r="H31" s="44"/>
       <c r="I31" s="1"/>
-      <c r="J31" s="50"/>
-      <c r="K31" s="50"/>
-      <c r="L31" s="50"/>
-      <c r="M31" s="50"/>
-      <c r="N31" s="50"/>
-      <c r="O31" s="50"/>
-      <c r="P31" s="50"/>
-      <c r="Q31" s="50"/>
-      <c r="R31" s="50"/>
-      <c r="S31" s="50"/>
-      <c r="T31" s="50"/>
-      <c r="U31" s="50"/>
-      <c r="V31" s="50"/>
-      <c r="W31" s="50"/>
-      <c r="X31" s="50"/>
+      <c r="J31" s="62"/>
+      <c r="K31" s="62"/>
+      <c r="L31" s="62"/>
+      <c r="M31" s="62"/>
+      <c r="N31" s="62"/>
+      <c r="O31" s="62"/>
+      <c r="P31" s="62"/>
+      <c r="Q31" s="62"/>
+      <c r="R31" s="62"/>
+      <c r="S31" s="62"/>
+      <c r="T31" s="62"/>
+      <c r="U31" s="62"/>
+      <c r="V31" s="62"/>
+      <c r="W31" s="62"/>
+      <c r="X31" s="62"/>
       <c r="Y31" s="1"/>
       <c r="Z31" s="1"/>
     </row>
@@ -2537,21 +2196,21 @@
       </c>
       <c r="H32" s="44"/>
       <c r="I32" s="1"/>
-      <c r="J32" s="50"/>
-      <c r="K32" s="50"/>
-      <c r="L32" s="50"/>
-      <c r="M32" s="50"/>
-      <c r="N32" s="50"/>
-      <c r="O32" s="50"/>
-      <c r="P32" s="50"/>
-      <c r="Q32" s="50"/>
-      <c r="R32" s="50"/>
-      <c r="S32" s="50"/>
-      <c r="T32" s="50"/>
-      <c r="U32" s="50"/>
-      <c r="V32" s="50"/>
-      <c r="W32" s="50"/>
-      <c r="X32" s="50"/>
+      <c r="J32" s="62"/>
+      <c r="K32" s="62"/>
+      <c r="L32" s="62"/>
+      <c r="M32" s="62"/>
+      <c r="N32" s="62"/>
+      <c r="O32" s="62"/>
+      <c r="P32" s="62"/>
+      <c r="Q32" s="62"/>
+      <c r="R32" s="62"/>
+      <c r="S32" s="62"/>
+      <c r="T32" s="62"/>
+      <c r="U32" s="62"/>
+      <c r="V32" s="62"/>
+      <c r="W32" s="62"/>
+      <c r="X32" s="62"/>
       <c r="Y32" s="1"/>
       <c r="Z32" s="1"/>
     </row>
@@ -2577,21 +2236,21 @@
       </c>
       <c r="H33" s="44"/>
       <c r="I33" s="1"/>
-      <c r="J33" s="50"/>
-      <c r="K33" s="50"/>
-      <c r="L33" s="50"/>
-      <c r="M33" s="50"/>
-      <c r="N33" s="50"/>
-      <c r="O33" s="50"/>
-      <c r="P33" s="50"/>
-      <c r="Q33" s="50"/>
-      <c r="R33" s="50"/>
-      <c r="S33" s="50"/>
-      <c r="T33" s="50"/>
-      <c r="U33" s="50"/>
-      <c r="V33" s="50"/>
-      <c r="W33" s="50"/>
-      <c r="X33" s="50"/>
+      <c r="J33" s="62"/>
+      <c r="K33" s="62"/>
+      <c r="L33" s="62"/>
+      <c r="M33" s="62"/>
+      <c r="N33" s="62"/>
+      <c r="O33" s="62"/>
+      <c r="P33" s="62"/>
+      <c r="Q33" s="62"/>
+      <c r="R33" s="62"/>
+      <c r="S33" s="62"/>
+      <c r="T33" s="62"/>
+      <c r="U33" s="62"/>
+      <c r="V33" s="62"/>
+      <c r="W33" s="62"/>
+      <c r="X33" s="62"/>
       <c r="Y33" s="1"/>
       <c r="Z33" s="1"/>
     </row>
@@ -2617,21 +2276,21 @@
       </c>
       <c r="H34" s="44"/>
       <c r="I34" s="1"/>
-      <c r="J34" s="50"/>
-      <c r="K34" s="50"/>
-      <c r="L34" s="50"/>
-      <c r="M34" s="50"/>
-      <c r="N34" s="50"/>
-      <c r="O34" s="50"/>
-      <c r="P34" s="50"/>
-      <c r="Q34" s="50"/>
-      <c r="R34" s="50"/>
-      <c r="S34" s="50"/>
-      <c r="T34" s="50"/>
-      <c r="U34" s="50"/>
-      <c r="V34" s="50"/>
-      <c r="W34" s="50"/>
-      <c r="X34" s="50"/>
+      <c r="J34" s="62"/>
+      <c r="K34" s="62"/>
+      <c r="L34" s="62"/>
+      <c r="M34" s="62"/>
+      <c r="N34" s="62"/>
+      <c r="O34" s="62"/>
+      <c r="P34" s="62"/>
+      <c r="Q34" s="62"/>
+      <c r="R34" s="62"/>
+      <c r="S34" s="62"/>
+      <c r="T34" s="62"/>
+      <c r="U34" s="62"/>
+      <c r="V34" s="62"/>
+      <c r="W34" s="62"/>
+      <c r="X34" s="62"/>
       <c r="Y34" s="1"/>
       <c r="Z34" s="1"/>
     </row>
@@ -2657,21 +2316,21 @@
         <v>44</v>
       </c>
       <c r="I35" s="1"/>
-      <c r="J35" s="50"/>
-      <c r="K35" s="50"/>
-      <c r="L35" s="50"/>
-      <c r="M35" s="50"/>
-      <c r="N35" s="50"/>
-      <c r="O35" s="50"/>
-      <c r="P35" s="50"/>
-      <c r="Q35" s="50"/>
-      <c r="R35" s="50"/>
-      <c r="S35" s="50"/>
-      <c r="T35" s="50"/>
-      <c r="U35" s="50"/>
-      <c r="V35" s="50"/>
-      <c r="W35" s="50"/>
-      <c r="X35" s="50"/>
+      <c r="J35" s="62"/>
+      <c r="K35" s="62"/>
+      <c r="L35" s="62"/>
+      <c r="M35" s="62"/>
+      <c r="N35" s="62"/>
+      <c r="O35" s="62"/>
+      <c r="P35" s="62"/>
+      <c r="Q35" s="62"/>
+      <c r="R35" s="62"/>
+      <c r="S35" s="62"/>
+      <c r="T35" s="62"/>
+      <c r="U35" s="62"/>
+      <c r="V35" s="62"/>
+      <c r="W35" s="62"/>
+      <c r="X35" s="62"/>
       <c r="Y35" s="1"/>
       <c r="Z35" s="1"/>
     </row>
@@ -2695,21 +2354,21 @@
       <c r="G36" s="46"/>
       <c r="H36" s="46"/>
       <c r="I36" s="1"/>
-      <c r="J36" s="50"/>
-      <c r="K36" s="50"/>
-      <c r="L36" s="50"/>
-      <c r="M36" s="50"/>
-      <c r="N36" s="50"/>
-      <c r="O36" s="50"/>
-      <c r="P36" s="50"/>
-      <c r="Q36" s="50"/>
-      <c r="R36" s="50"/>
-      <c r="S36" s="50"/>
-      <c r="T36" s="50"/>
-      <c r="U36" s="50"/>
-      <c r="V36" s="50"/>
-      <c r="W36" s="50"/>
-      <c r="X36" s="50"/>
+      <c r="J36" s="62"/>
+      <c r="K36" s="62"/>
+      <c r="L36" s="62"/>
+      <c r="M36" s="62"/>
+      <c r="N36" s="62"/>
+      <c r="O36" s="62"/>
+      <c r="P36" s="62"/>
+      <c r="Q36" s="62"/>
+      <c r="R36" s="62"/>
+      <c r="S36" s="62"/>
+      <c r="T36" s="62"/>
+      <c r="U36" s="62"/>
+      <c r="V36" s="62"/>
+      <c r="W36" s="62"/>
+      <c r="X36" s="62"/>
       <c r="Y36" s="1"/>
       <c r="Z36" s="1"/>
     </row>
@@ -2725,21 +2384,21 @@
       <c r="G37" s="46"/>
       <c r="H37" s="46"/>
       <c r="I37" s="1"/>
-      <c r="J37" s="50"/>
-      <c r="K37" s="50"/>
-      <c r="L37" s="50"/>
-      <c r="M37" s="50"/>
-      <c r="N37" s="50"/>
-      <c r="O37" s="50"/>
-      <c r="P37" s="50"/>
-      <c r="Q37" s="50"/>
-      <c r="R37" s="50"/>
-      <c r="S37" s="50"/>
-      <c r="T37" s="50"/>
-      <c r="U37" s="50"/>
-      <c r="V37" s="50"/>
-      <c r="W37" s="50"/>
-      <c r="X37" s="50"/>
+      <c r="J37" s="62"/>
+      <c r="K37" s="62"/>
+      <c r="L37" s="62"/>
+      <c r="M37" s="62"/>
+      <c r="N37" s="62"/>
+      <c r="O37" s="62"/>
+      <c r="P37" s="62"/>
+      <c r="Q37" s="62"/>
+      <c r="R37" s="62"/>
+      <c r="S37" s="62"/>
+      <c r="T37" s="62"/>
+      <c r="U37" s="62"/>
+      <c r="V37" s="62"/>
+      <c r="W37" s="62"/>
+      <c r="X37" s="62"/>
       <c r="Y37" s="1"/>
       <c r="Z37" s="1"/>
     </row>
@@ -2763,21 +2422,21 @@
       <c r="G38" s="46"/>
       <c r="H38" s="46"/>
       <c r="I38" s="1"/>
-      <c r="J38" s="50"/>
-      <c r="K38" s="50"/>
-      <c r="L38" s="50"/>
-      <c r="M38" s="50"/>
-      <c r="N38" s="50"/>
-      <c r="O38" s="50"/>
-      <c r="P38" s="50"/>
-      <c r="Q38" s="50"/>
-      <c r="R38" s="50"/>
-      <c r="S38" s="50"/>
-      <c r="T38" s="50"/>
-      <c r="U38" s="50"/>
-      <c r="V38" s="50"/>
-      <c r="W38" s="50"/>
-      <c r="X38" s="50"/>
+      <c r="J38" s="62"/>
+      <c r="K38" s="62"/>
+      <c r="L38" s="62"/>
+      <c r="M38" s="62"/>
+      <c r="N38" s="62"/>
+      <c r="O38" s="62"/>
+      <c r="P38" s="62"/>
+      <c r="Q38" s="62"/>
+      <c r="R38" s="62"/>
+      <c r="S38" s="62"/>
+      <c r="T38" s="62"/>
+      <c r="U38" s="62"/>
+      <c r="V38" s="62"/>
+      <c r="W38" s="62"/>
+      <c r="X38" s="62"/>
       <c r="Y38" s="1"/>
       <c r="Z38" s="1"/>
     </row>
@@ -2801,21 +2460,21 @@
       <c r="G39" s="46"/>
       <c r="H39" s="46"/>
       <c r="I39" s="1"/>
-      <c r="J39" s="50"/>
-      <c r="K39" s="50"/>
-      <c r="L39" s="50"/>
-      <c r="M39" s="50"/>
-      <c r="N39" s="50"/>
-      <c r="O39" s="50"/>
-      <c r="P39" s="50"/>
-      <c r="Q39" s="50"/>
-      <c r="R39" s="50"/>
-      <c r="S39" s="50"/>
-      <c r="T39" s="50"/>
-      <c r="U39" s="50"/>
-      <c r="V39" s="50"/>
-      <c r="W39" s="50"/>
-      <c r="X39" s="50"/>
+      <c r="J39" s="62"/>
+      <c r="K39" s="62"/>
+      <c r="L39" s="62"/>
+      <c r="M39" s="62"/>
+      <c r="N39" s="62"/>
+      <c r="O39" s="62"/>
+      <c r="P39" s="62"/>
+      <c r="Q39" s="62"/>
+      <c r="R39" s="62"/>
+      <c r="S39" s="62"/>
+      <c r="T39" s="62"/>
+      <c r="U39" s="62"/>
+      <c r="V39" s="62"/>
+      <c r="W39" s="62"/>
+      <c r="X39" s="62"/>
       <c r="Y39" s="1"/>
       <c r="Z39" s="1"/>
     </row>
@@ -2839,21 +2498,21 @@
       <c r="G40" s="46"/>
       <c r="H40" s="46"/>
       <c r="I40" s="1"/>
-      <c r="J40" s="50"/>
-      <c r="K40" s="50"/>
-      <c r="L40" s="50"/>
-      <c r="M40" s="50"/>
-      <c r="N40" s="50"/>
-      <c r="O40" s="50"/>
-      <c r="P40" s="50"/>
-      <c r="Q40" s="50"/>
-      <c r="R40" s="50"/>
-      <c r="S40" s="50"/>
-      <c r="T40" s="50"/>
-      <c r="U40" s="50"/>
-      <c r="V40" s="50"/>
-      <c r="W40" s="50"/>
-      <c r="X40" s="50"/>
+      <c r="J40" s="62"/>
+      <c r="K40" s="62"/>
+      <c r="L40" s="62"/>
+      <c r="M40" s="62"/>
+      <c r="N40" s="62"/>
+      <c r="O40" s="62"/>
+      <c r="P40" s="62"/>
+      <c r="Q40" s="62"/>
+      <c r="R40" s="62"/>
+      <c r="S40" s="62"/>
+      <c r="T40" s="62"/>
+      <c r="U40" s="62"/>
+      <c r="V40" s="62"/>
+      <c r="W40" s="62"/>
+      <c r="X40" s="62"/>
       <c r="Y40" s="1"/>
       <c r="Z40" s="1"/>
     </row>
@@ -28261,7 +27920,6 @@
   <phoneticPr fontId="10" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="landscape"/>
-  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -28271,297 +27929,297 @@
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:54" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="53" t="s">
+      <c r="A1" s="49" t="s">
         <v>50</v>
       </c>
-      <c r="B1" s="54" t="s">
+      <c r="B1" s="50" t="s">
         <v>45</v>
       </c>
-      <c r="C1" s="54" t="s">
+      <c r="C1" s="50" t="s">
         <v>46</v>
       </c>
-      <c r="D1" s="54" t="s">
+      <c r="D1" s="50" t="s">
         <v>47</v>
       </c>
-      <c r="E1" s="54" t="s">
+      <c r="E1" s="50" t="s">
         <v>48</v>
       </c>
-      <c r="F1" s="54" t="s">
+      <c r="F1" s="50" t="s">
         <v>49</v>
       </c>
-      <c r="G1" s="55"/>
-      <c r="H1" s="56"/>
-      <c r="I1" s="56"/>
-      <c r="J1" s="56"/>
-      <c r="K1" s="56"/>
-      <c r="L1" s="57"/>
-      <c r="M1" s="55"/>
-      <c r="N1" s="58"/>
-      <c r="O1" s="58"/>
-      <c r="P1" s="58"/>
-      <c r="Q1" s="58"/>
-      <c r="R1" s="59"/>
-      <c r="S1" s="55"/>
-      <c r="T1" s="58"/>
-      <c r="U1" s="58"/>
-      <c r="V1" s="58"/>
-      <c r="W1" s="58"/>
-      <c r="X1" s="59"/>
-      <c r="Y1" s="55"/>
-      <c r="Z1" s="58"/>
-      <c r="AA1" s="58"/>
-      <c r="AB1" s="58"/>
-      <c r="AC1" s="58"/>
-      <c r="AD1" s="59"/>
-      <c r="AE1" s="55"/>
-      <c r="AF1" s="56"/>
-      <c r="AG1" s="58"/>
-      <c r="AH1" s="56"/>
-      <c r="AI1" s="58"/>
-      <c r="AJ1" s="57"/>
-      <c r="AK1" s="55"/>
-      <c r="AL1" s="58"/>
-      <c r="AM1" s="58"/>
-      <c r="AN1" s="58"/>
-      <c r="AO1" s="58"/>
-      <c r="AP1" s="59"/>
-      <c r="AQ1" s="55"/>
-      <c r="AR1" s="58"/>
-      <c r="AS1" s="58"/>
-      <c r="AT1" s="58"/>
-      <c r="AU1" s="58"/>
-      <c r="AV1" s="59"/>
-      <c r="AW1" s="55"/>
-      <c r="AX1" s="58"/>
-      <c r="AY1" s="56"/>
-      <c r="AZ1" s="58"/>
-      <c r="BA1" s="56"/>
-      <c r="BB1" s="59"/>
+      <c r="G1" s="51"/>
+      <c r="H1" s="52"/>
+      <c r="I1" s="52"/>
+      <c r="J1" s="52"/>
+      <c r="K1" s="52"/>
+      <c r="L1" s="53"/>
+      <c r="M1" s="51"/>
+      <c r="N1" s="54"/>
+      <c r="O1" s="54"/>
+      <c r="P1" s="54"/>
+      <c r="Q1" s="54"/>
+      <c r="R1" s="55"/>
+      <c r="S1" s="51"/>
+      <c r="T1" s="54"/>
+      <c r="U1" s="54"/>
+      <c r="V1" s="54"/>
+      <c r="W1" s="54"/>
+      <c r="X1" s="55"/>
+      <c r="Y1" s="51"/>
+      <c r="Z1" s="54"/>
+      <c r="AA1" s="54"/>
+      <c r="AB1" s="54"/>
+      <c r="AC1" s="54"/>
+      <c r="AD1" s="55"/>
+      <c r="AE1" s="51"/>
+      <c r="AF1" s="52"/>
+      <c r="AG1" s="54"/>
+      <c r="AH1" s="52"/>
+      <c r="AI1" s="54"/>
+      <c r="AJ1" s="53"/>
+      <c r="AK1" s="51"/>
+      <c r="AL1" s="54"/>
+      <c r="AM1" s="54"/>
+      <c r="AN1" s="54"/>
+      <c r="AO1" s="54"/>
+      <c r="AP1" s="55"/>
+      <c r="AQ1" s="51"/>
+      <c r="AR1" s="54"/>
+      <c r="AS1" s="54"/>
+      <c r="AT1" s="54"/>
+      <c r="AU1" s="54"/>
+      <c r="AV1" s="55"/>
+      <c r="AW1" s="51"/>
+      <c r="AX1" s="54"/>
+      <c r="AY1" s="52"/>
+      <c r="AZ1" s="54"/>
+      <c r="BA1" s="52"/>
+      <c r="BB1" s="55"/>
     </row>
     <row r="2" spans="1:54" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="60">
+      <c r="A2" s="56">
         <v>0</v>
       </c>
-      <c r="B2" s="61">
+      <c r="B2" s="57">
         <v>0</v>
       </c>
-      <c r="C2" s="61">
+      <c r="C2" s="57">
         <v>0</v>
       </c>
-      <c r="D2" s="61">
+      <c r="D2" s="57">
         <v>0</v>
       </c>
-      <c r="E2" s="61">
+      <c r="E2" s="57">
         <v>0</v>
       </c>
-      <c r="F2" s="61">
+      <c r="F2" s="57">
         <v>0</v>
       </c>
-      <c r="G2" s="55"/>
-      <c r="H2" s="58"/>
-      <c r="I2" s="58"/>
-      <c r="J2" s="58"/>
-      <c r="K2" s="58"/>
-      <c r="L2" s="59"/>
-      <c r="M2" s="55"/>
-      <c r="N2" s="56"/>
-      <c r="O2" s="56"/>
-      <c r="P2" s="56"/>
-      <c r="Q2" s="56"/>
-      <c r="R2" s="57"/>
-      <c r="S2" s="55"/>
-      <c r="T2" s="58"/>
-      <c r="U2" s="58"/>
-      <c r="V2" s="58"/>
-      <c r="W2" s="58"/>
-      <c r="X2" s="59"/>
-      <c r="Y2" s="55"/>
-      <c r="Z2" s="58"/>
-      <c r="AA2" s="58"/>
-      <c r="AB2" s="58"/>
-      <c r="AC2" s="58"/>
-      <c r="AD2" s="59"/>
-      <c r="AE2" s="55"/>
-      <c r="AF2" s="58"/>
-      <c r="AG2" s="56"/>
-      <c r="AH2" s="58"/>
-      <c r="AI2" s="56"/>
-      <c r="AJ2" s="59"/>
-      <c r="AK2" s="55"/>
-      <c r="AL2" s="56"/>
-      <c r="AM2" s="58"/>
-      <c r="AN2" s="56"/>
-      <c r="AO2" s="58"/>
-      <c r="AP2" s="57"/>
-      <c r="AQ2" s="55"/>
-      <c r="AR2" s="58"/>
-      <c r="AS2" s="58"/>
-      <c r="AT2" s="58"/>
-      <c r="AU2" s="58"/>
-      <c r="AV2" s="59"/>
-      <c r="AW2" s="55"/>
-      <c r="AX2" s="56"/>
-      <c r="AY2" s="58"/>
-      <c r="AZ2" s="56"/>
-      <c r="BA2" s="58"/>
-      <c r="BB2" s="57"/>
+      <c r="G2" s="51"/>
+      <c r="H2" s="54"/>
+      <c r="I2" s="54"/>
+      <c r="J2" s="54"/>
+      <c r="K2" s="54"/>
+      <c r="L2" s="55"/>
+      <c r="M2" s="51"/>
+      <c r="N2" s="52"/>
+      <c r="O2" s="52"/>
+      <c r="P2" s="52"/>
+      <c r="Q2" s="52"/>
+      <c r="R2" s="53"/>
+      <c r="S2" s="51"/>
+      <c r="T2" s="54"/>
+      <c r="U2" s="54"/>
+      <c r="V2" s="54"/>
+      <c r="W2" s="54"/>
+      <c r="X2" s="55"/>
+      <c r="Y2" s="51"/>
+      <c r="Z2" s="54"/>
+      <c r="AA2" s="54"/>
+      <c r="AB2" s="54"/>
+      <c r="AC2" s="54"/>
+      <c r="AD2" s="55"/>
+      <c r="AE2" s="51"/>
+      <c r="AF2" s="54"/>
+      <c r="AG2" s="52"/>
+      <c r="AH2" s="54"/>
+      <c r="AI2" s="52"/>
+      <c r="AJ2" s="55"/>
+      <c r="AK2" s="51"/>
+      <c r="AL2" s="52"/>
+      <c r="AM2" s="54"/>
+      <c r="AN2" s="52"/>
+      <c r="AO2" s="54"/>
+      <c r="AP2" s="53"/>
+      <c r="AQ2" s="51"/>
+      <c r="AR2" s="54"/>
+      <c r="AS2" s="54"/>
+      <c r="AT2" s="54"/>
+      <c r="AU2" s="54"/>
+      <c r="AV2" s="55"/>
+      <c r="AW2" s="51"/>
+      <c r="AX2" s="52"/>
+      <c r="AY2" s="54"/>
+      <c r="AZ2" s="52"/>
+      <c r="BA2" s="54"/>
+      <c r="BB2" s="53"/>
     </row>
     <row r="3" spans="1:54" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="60">
+      <c r="A3" s="56">
         <v>1</v>
       </c>
-      <c r="B3" s="61">
+      <c r="B3" s="57">
         <v>1</v>
       </c>
-      <c r="C3" s="61">
+      <c r="C3" s="57">
         <v>1</v>
       </c>
-      <c r="D3" s="61">
+      <c r="D3" s="57">
         <v>1</v>
       </c>
-      <c r="E3" s="61">
+      <c r="E3" s="57">
         <v>1</v>
       </c>
-      <c r="F3" s="61">
+      <c r="F3" s="57">
         <v>1</v>
       </c>
-      <c r="G3" s="55"/>
-      <c r="H3" s="58"/>
-      <c r="I3" s="58"/>
-      <c r="J3" s="58"/>
-      <c r="K3" s="58"/>
-      <c r="L3" s="59"/>
-      <c r="M3" s="55"/>
-      <c r="N3" s="58"/>
-      <c r="O3" s="58"/>
-      <c r="P3" s="58"/>
-      <c r="Q3" s="58"/>
-      <c r="R3" s="59"/>
-      <c r="S3" s="55"/>
-      <c r="T3" s="56"/>
-      <c r="U3" s="56"/>
-      <c r="V3" s="56"/>
-      <c r="W3" s="56"/>
-      <c r="X3" s="57"/>
-      <c r="Y3" s="55"/>
-      <c r="Z3" s="58"/>
-      <c r="AA3" s="58"/>
-      <c r="AB3" s="58"/>
-      <c r="AC3" s="58"/>
-      <c r="AD3" s="59"/>
-      <c r="AE3" s="55"/>
-      <c r="AF3" s="58"/>
-      <c r="AG3" s="58"/>
-      <c r="AH3" s="58"/>
-      <c r="AI3" s="58"/>
-      <c r="AJ3" s="59"/>
-      <c r="AK3" s="55"/>
-      <c r="AL3" s="58"/>
-      <c r="AM3" s="56"/>
-      <c r="AN3" s="58"/>
-      <c r="AO3" s="56"/>
-      <c r="AP3" s="59"/>
-      <c r="AQ3" s="55"/>
-      <c r="AR3" s="56"/>
-      <c r="AS3" s="58"/>
-      <c r="AT3" s="56"/>
-      <c r="AU3" s="58"/>
-      <c r="AV3" s="57"/>
-      <c r="AW3" s="55"/>
-      <c r="AX3" s="58"/>
-      <c r="AY3" s="58"/>
-      <c r="AZ3" s="58"/>
-      <c r="BA3" s="58"/>
-      <c r="BB3" s="59"/>
+      <c r="G3" s="51"/>
+      <c r="H3" s="54"/>
+      <c r="I3" s="54"/>
+      <c r="J3" s="54"/>
+      <c r="K3" s="54"/>
+      <c r="L3" s="55"/>
+      <c r="M3" s="51"/>
+      <c r="N3" s="54"/>
+      <c r="O3" s="54"/>
+      <c r="P3" s="54"/>
+      <c r="Q3" s="54"/>
+      <c r="R3" s="55"/>
+      <c r="S3" s="51"/>
+      <c r="T3" s="52"/>
+      <c r="U3" s="52"/>
+      <c r="V3" s="52"/>
+      <c r="W3" s="52"/>
+      <c r="X3" s="53"/>
+      <c r="Y3" s="51"/>
+      <c r="Z3" s="54"/>
+      <c r="AA3" s="54"/>
+      <c r="AB3" s="54"/>
+      <c r="AC3" s="54"/>
+      <c r="AD3" s="55"/>
+      <c r="AE3" s="51"/>
+      <c r="AF3" s="54"/>
+      <c r="AG3" s="54"/>
+      <c r="AH3" s="54"/>
+      <c r="AI3" s="54"/>
+      <c r="AJ3" s="55"/>
+      <c r="AK3" s="51"/>
+      <c r="AL3" s="54"/>
+      <c r="AM3" s="52"/>
+      <c r="AN3" s="54"/>
+      <c r="AO3" s="52"/>
+      <c r="AP3" s="55"/>
+      <c r="AQ3" s="51"/>
+      <c r="AR3" s="52"/>
+      <c r="AS3" s="54"/>
+      <c r="AT3" s="52"/>
+      <c r="AU3" s="54"/>
+      <c r="AV3" s="53"/>
+      <c r="AW3" s="51"/>
+      <c r="AX3" s="54"/>
+      <c r="AY3" s="54"/>
+      <c r="AZ3" s="54"/>
+      <c r="BA3" s="54"/>
+      <c r="BB3" s="55"/>
     </row>
     <row r="4" spans="1:54" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="60">
+      <c r="A4" s="56">
         <v>2</v>
       </c>
-      <c r="B4" s="61">
+      <c r="B4" s="57">
         <v>2</v>
       </c>
-      <c r="C4" s="61">
+      <c r="C4" s="57">
         <v>2</v>
       </c>
-      <c r="D4" s="61">
+      <c r="D4" s="57">
         <v>2</v>
       </c>
-      <c r="E4" s="61">
+      <c r="E4" s="57">
         <v>2</v>
       </c>
-      <c r="F4" s="61">
+      <c r="F4" s="57">
         <v>2</v>
       </c>
-      <c r="G4" s="55"/>
-      <c r="H4" s="58"/>
-      <c r="I4" s="58"/>
-      <c r="J4" s="58"/>
-      <c r="K4" s="58"/>
-      <c r="L4" s="59"/>
-      <c r="M4" s="55"/>
-      <c r="N4" s="58"/>
-      <c r="O4" s="58"/>
-      <c r="P4" s="58"/>
-      <c r="Q4" s="58"/>
-      <c r="R4" s="59"/>
-      <c r="S4" s="55"/>
-      <c r="T4" s="58"/>
-      <c r="U4" s="58"/>
-      <c r="V4" s="58"/>
-      <c r="W4" s="58"/>
-      <c r="X4" s="59"/>
-      <c r="Y4" s="55"/>
-      <c r="Z4" s="56"/>
-      <c r="AA4" s="56"/>
-      <c r="AB4" s="56"/>
-      <c r="AC4" s="56"/>
-      <c r="AD4" s="57"/>
-      <c r="AE4" s="55"/>
-      <c r="AF4" s="58"/>
-      <c r="AG4" s="58"/>
-      <c r="AH4" s="58"/>
-      <c r="AI4" s="58"/>
-      <c r="AJ4" s="59"/>
-      <c r="AK4" s="55"/>
-      <c r="AL4" s="58"/>
-      <c r="AM4" s="58"/>
-      <c r="AN4" s="58"/>
-      <c r="AO4" s="58"/>
-      <c r="AP4" s="59"/>
-      <c r="AQ4" s="55"/>
-      <c r="AR4" s="58"/>
-      <c r="AS4" s="56"/>
-      <c r="AT4" s="58"/>
-      <c r="AU4" s="56"/>
-      <c r="AV4" s="59"/>
-      <c r="AW4" s="55"/>
-      <c r="AX4" s="58"/>
-      <c r="AY4" s="58"/>
-      <c r="AZ4" s="58"/>
-      <c r="BA4" s="58"/>
-      <c r="BB4" s="59"/>
+      <c r="G4" s="51"/>
+      <c r="H4" s="54"/>
+      <c r="I4" s="54"/>
+      <c r="J4" s="54"/>
+      <c r="K4" s="54"/>
+      <c r="L4" s="55"/>
+      <c r="M4" s="51"/>
+      <c r="N4" s="54"/>
+      <c r="O4" s="54"/>
+      <c r="P4" s="54"/>
+      <c r="Q4" s="54"/>
+      <c r="R4" s="55"/>
+      <c r="S4" s="51"/>
+      <c r="T4" s="54"/>
+      <c r="U4" s="54"/>
+      <c r="V4" s="54"/>
+      <c r="W4" s="54"/>
+      <c r="X4" s="55"/>
+      <c r="Y4" s="51"/>
+      <c r="Z4" s="52"/>
+      <c r="AA4" s="52"/>
+      <c r="AB4" s="52"/>
+      <c r="AC4" s="52"/>
+      <c r="AD4" s="53"/>
+      <c r="AE4" s="51"/>
+      <c r="AF4" s="54"/>
+      <c r="AG4" s="54"/>
+      <c r="AH4" s="54"/>
+      <c r="AI4" s="54"/>
+      <c r="AJ4" s="55"/>
+      <c r="AK4" s="51"/>
+      <c r="AL4" s="54"/>
+      <c r="AM4" s="54"/>
+      <c r="AN4" s="54"/>
+      <c r="AO4" s="54"/>
+      <c r="AP4" s="55"/>
+      <c r="AQ4" s="51"/>
+      <c r="AR4" s="54"/>
+      <c r="AS4" s="52"/>
+      <c r="AT4" s="54"/>
+      <c r="AU4" s="52"/>
+      <c r="AV4" s="55"/>
+      <c r="AW4" s="51"/>
+      <c r="AX4" s="54"/>
+      <c r="AY4" s="54"/>
+      <c r="AZ4" s="54"/>
+      <c r="BA4" s="54"/>
+      <c r="BB4" s="55"/>
     </row>
     <row r="5" spans="1:54" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="60">
+      <c r="A5" s="56">
         <v>3</v>
       </c>
-      <c r="B5" s="61">
+      <c r="B5" s="57">
         <v>3</v>
       </c>
-      <c r="C5" s="61">
+      <c r="C5" s="57">
         <v>3</v>
       </c>
-      <c r="D5" s="61">
+      <c r="D5" s="57">
         <v>3</v>
       </c>
-      <c r="E5" s="61">
+      <c r="E5" s="57">
         <v>3</v>
       </c>
-      <c r="F5" s="61">
+      <c r="F5" s="57">
         <v>3</v>
       </c>
-      <c r="G5" s="55"/>
+      <c r="G5" s="51"/>
       <c r="H5" s="63">
         <v>1</v>
       </c>
@@ -28569,7 +28227,7 @@
       <c r="J5" s="64"/>
       <c r="K5" s="64"/>
       <c r="L5" s="65"/>
-      <c r="M5" s="55"/>
+      <c r="M5" s="51"/>
       <c r="N5" s="63">
         <v>2</v>
       </c>
@@ -28577,7 +28235,7 @@
       <c r="P5" s="64"/>
       <c r="Q5" s="64"/>
       <c r="R5" s="65"/>
-      <c r="S5" s="55"/>
+      <c r="S5" s="51"/>
       <c r="T5" s="63">
         <v>3</v>
       </c>
@@ -28585,7 +28243,7 @@
       <c r="V5" s="64"/>
       <c r="W5" s="64"/>
       <c r="X5" s="65"/>
-      <c r="Y5" s="55"/>
+      <c r="Y5" s="51"/>
       <c r="Z5" s="63">
         <v>4</v>
       </c>
@@ -28593,7 +28251,7 @@
       <c r="AB5" s="64"/>
       <c r="AC5" s="64"/>
       <c r="AD5" s="65"/>
-      <c r="AE5" s="55"/>
+      <c r="AE5" s="51"/>
       <c r="AF5" s="63">
         <v>5</v>
       </c>
@@ -28601,7 +28259,7 @@
       <c r="AH5" s="64"/>
       <c r="AI5" s="64"/>
       <c r="AJ5" s="65"/>
-      <c r="AK5" s="55"/>
+      <c r="AK5" s="51"/>
       <c r="AL5" s="63">
         <v>6</v>
       </c>
@@ -28609,7 +28267,7 @@
       <c r="AN5" s="64"/>
       <c r="AO5" s="64"/>
       <c r="AP5" s="65"/>
-      <c r="AQ5" s="55"/>
+      <c r="AQ5" s="51"/>
       <c r="AR5" s="63">
         <v>7</v>
       </c>
@@ -28617,7 +28275,7 @@
       <c r="AT5" s="64"/>
       <c r="AU5" s="64"/>
       <c r="AV5" s="65"/>
-      <c r="AW5" s="55"/>
+      <c r="AW5" s="51"/>
       <c r="AX5" s="63">
         <v>8</v>
       </c>
@@ -28627,433 +28285,433 @@
       <c r="BB5" s="65"/>
     </row>
     <row r="6" spans="1:54" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="60">
+      <c r="A6" s="56">
         <v>4</v>
       </c>
-      <c r="B6" s="61">
+      <c r="B6" s="57">
         <v>0</v>
       </c>
-      <c r="C6" s="61">
+      <c r="C6" s="57">
         <v>1</v>
       </c>
-      <c r="D6" s="61">
+      <c r="D6" s="57">
         <v>0</v>
       </c>
-      <c r="E6" s="61">
+      <c r="E6" s="57">
         <v>1</v>
       </c>
-      <c r="F6" s="61">
+      <c r="F6" s="57">
         <v>0</v>
       </c>
-      <c r="G6" s="52"/>
-      <c r="H6" s="52"/>
-      <c r="I6" s="52"/>
-      <c r="J6" s="52"/>
-      <c r="K6" s="52"/>
-      <c r="L6" s="52"/>
-      <c r="M6" s="52"/>
-      <c r="N6" s="52"/>
-      <c r="O6" s="52"/>
-      <c r="P6" s="52"/>
-      <c r="Q6" s="52"/>
-      <c r="R6" s="52"/>
-      <c r="S6" s="52"/>
-      <c r="T6" s="52"/>
-      <c r="U6" s="52"/>
-      <c r="V6" s="52"/>
-      <c r="W6" s="52"/>
-      <c r="X6" s="52"/>
-      <c r="Y6" s="52"/>
-      <c r="Z6" s="52"/>
-      <c r="AA6" s="52"/>
-      <c r="AB6" s="52"/>
-      <c r="AC6" s="52"/>
-      <c r="AD6" s="52"/>
-      <c r="AE6" s="52"/>
-      <c r="AF6" s="52"/>
-      <c r="AG6" s="52"/>
-      <c r="AH6" s="52"/>
-      <c r="AI6" s="52"/>
-      <c r="AJ6" s="52"/>
-      <c r="AK6" s="52"/>
-      <c r="AL6" s="52"/>
-      <c r="AM6" s="52"/>
-      <c r="AN6" s="52"/>
-      <c r="AO6" s="52"/>
-      <c r="AP6" s="52"/>
-      <c r="AQ6" s="52"/>
-      <c r="AR6" s="52"/>
-      <c r="AS6" s="52"/>
-      <c r="AT6" s="52"/>
-      <c r="AU6" s="52"/>
-      <c r="AV6" s="52"/>
-      <c r="AW6" s="52"/>
-      <c r="AX6" s="52"/>
-      <c r="AY6" s="52"/>
-      <c r="AZ6" s="52"/>
-      <c r="BA6" s="52"/>
-      <c r="BB6" s="52"/>
+      <c r="G6" s="48"/>
+      <c r="H6" s="48"/>
+      <c r="I6" s="48"/>
+      <c r="J6" s="48"/>
+      <c r="K6" s="48"/>
+      <c r="L6" s="48"/>
+      <c r="M6" s="48"/>
+      <c r="N6" s="48"/>
+      <c r="O6" s="48"/>
+      <c r="P6" s="48"/>
+      <c r="Q6" s="48"/>
+      <c r="R6" s="48"/>
+      <c r="S6" s="48"/>
+      <c r="T6" s="48"/>
+      <c r="U6" s="48"/>
+      <c r="V6" s="48"/>
+      <c r="W6" s="48"/>
+      <c r="X6" s="48"/>
+      <c r="Y6" s="48"/>
+      <c r="Z6" s="48"/>
+      <c r="AA6" s="48"/>
+      <c r="AB6" s="48"/>
+      <c r="AC6" s="48"/>
+      <c r="AD6" s="48"/>
+      <c r="AE6" s="48"/>
+      <c r="AF6" s="48"/>
+      <c r="AG6" s="48"/>
+      <c r="AH6" s="48"/>
+      <c r="AI6" s="48"/>
+      <c r="AJ6" s="48"/>
+      <c r="AK6" s="48"/>
+      <c r="AL6" s="48"/>
+      <c r="AM6" s="48"/>
+      <c r="AN6" s="48"/>
+      <c r="AO6" s="48"/>
+      <c r="AP6" s="48"/>
+      <c r="AQ6" s="48"/>
+      <c r="AR6" s="48"/>
+      <c r="AS6" s="48"/>
+      <c r="AT6" s="48"/>
+      <c r="AU6" s="48"/>
+      <c r="AV6" s="48"/>
+      <c r="AW6" s="48"/>
+      <c r="AX6" s="48"/>
+      <c r="AY6" s="48"/>
+      <c r="AZ6" s="48"/>
+      <c r="BA6" s="48"/>
+      <c r="BB6" s="48"/>
     </row>
     <row r="7" spans="1:54" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="60">
+      <c r="A7" s="56">
         <v>5</v>
       </c>
-      <c r="B7" s="61">
+      <c r="B7" s="57">
         <v>1</v>
       </c>
-      <c r="C7" s="61">
+      <c r="C7" s="57">
         <v>2</v>
       </c>
-      <c r="D7" s="61">
+      <c r="D7" s="57">
         <v>1</v>
       </c>
-      <c r="E7" s="61">
+      <c r="E7" s="57">
         <v>2</v>
       </c>
-      <c r="F7" s="61">
+      <c r="F7" s="57">
         <v>1</v>
       </c>
-      <c r="G7" s="52"/>
-      <c r="H7" s="51"/>
-      <c r="I7" s="51"/>
-      <c r="J7" s="51"/>
-      <c r="K7" s="51"/>
-      <c r="L7" s="51"/>
-      <c r="M7" s="52"/>
-      <c r="N7" s="51"/>
-      <c r="O7" s="51"/>
-      <c r="P7" s="51"/>
-      <c r="Q7" s="51"/>
-      <c r="R7" s="51"/>
-      <c r="S7" s="52"/>
-      <c r="T7" s="51"/>
-      <c r="U7" s="51"/>
-      <c r="V7" s="51"/>
-      <c r="W7" s="51"/>
-      <c r="X7" s="51"/>
-      <c r="Y7" s="52"/>
-      <c r="Z7" s="51"/>
-      <c r="AA7" s="51"/>
-      <c r="AB7" s="51"/>
-      <c r="AC7" s="51"/>
-      <c r="AD7" s="51"/>
-      <c r="AE7" s="52"/>
-      <c r="AF7" s="51"/>
-      <c r="AG7" s="51"/>
-      <c r="AH7" s="51"/>
-      <c r="AI7" s="51"/>
-      <c r="AJ7" s="51"/>
-      <c r="AK7" s="52"/>
-      <c r="AL7" s="51"/>
-      <c r="AM7" s="51"/>
-      <c r="AN7" s="51"/>
-      <c r="AO7" s="51"/>
-      <c r="AP7" s="51"/>
-      <c r="AQ7" s="52"/>
-      <c r="AR7" s="52"/>
-      <c r="AS7" s="52"/>
-      <c r="AT7" s="52"/>
-      <c r="AU7" s="52"/>
-      <c r="AV7" s="52"/>
-      <c r="AW7" s="52"/>
-      <c r="AX7" s="52"/>
-      <c r="AY7" s="52"/>
-      <c r="AZ7" s="52"/>
-      <c r="BA7" s="52"/>
-      <c r="BB7" s="52"/>
+      <c r="G7" s="48"/>
+      <c r="H7" s="47"/>
+      <c r="I7" s="47"/>
+      <c r="J7" s="47"/>
+      <c r="K7" s="47"/>
+      <c r="L7" s="47"/>
+      <c r="M7" s="48"/>
+      <c r="N7" s="47"/>
+      <c r="O7" s="47"/>
+      <c r="P7" s="47"/>
+      <c r="Q7" s="47"/>
+      <c r="R7" s="47"/>
+      <c r="S7" s="48"/>
+      <c r="T7" s="47"/>
+      <c r="U7" s="47"/>
+      <c r="V7" s="47"/>
+      <c r="W7" s="47"/>
+      <c r="X7" s="47"/>
+      <c r="Y7" s="48"/>
+      <c r="Z7" s="47"/>
+      <c r="AA7" s="47"/>
+      <c r="AB7" s="47"/>
+      <c r="AC7" s="47"/>
+      <c r="AD7" s="47"/>
+      <c r="AE7" s="48"/>
+      <c r="AF7" s="47"/>
+      <c r="AG7" s="47"/>
+      <c r="AH7" s="47"/>
+      <c r="AI7" s="47"/>
+      <c r="AJ7" s="47"/>
+      <c r="AK7" s="48"/>
+      <c r="AL7" s="47"/>
+      <c r="AM7" s="47"/>
+      <c r="AN7" s="47"/>
+      <c r="AO7" s="47"/>
+      <c r="AP7" s="47"/>
+      <c r="AQ7" s="48"/>
+      <c r="AR7" s="48"/>
+      <c r="AS7" s="48"/>
+      <c r="AT7" s="48"/>
+      <c r="AU7" s="48"/>
+      <c r="AV7" s="48"/>
+      <c r="AW7" s="48"/>
+      <c r="AX7" s="48"/>
+      <c r="AY7" s="48"/>
+      <c r="AZ7" s="48"/>
+      <c r="BA7" s="48"/>
+      <c r="BB7" s="48"/>
     </row>
     <row r="8" spans="1:54" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="60">
+      <c r="A8" s="56">
         <v>6</v>
       </c>
-      <c r="B8" s="61">
+      <c r="B8" s="57">
         <v>2</v>
       </c>
-      <c r="C8" s="61">
+      <c r="C8" s="57">
         <v>3</v>
       </c>
-      <c r="D8" s="61">
+      <c r="D8" s="57">
         <v>2</v>
       </c>
-      <c r="E8" s="61">
+      <c r="E8" s="57">
         <v>3</v>
       </c>
-      <c r="F8" s="61">
+      <c r="F8" s="57">
         <v>2</v>
       </c>
-      <c r="G8" s="55"/>
-      <c r="H8" s="58"/>
-      <c r="I8" s="58"/>
-      <c r="J8" s="58"/>
-      <c r="K8" s="58"/>
-      <c r="L8" s="59"/>
-      <c r="M8" s="55"/>
-      <c r="N8" s="58"/>
-      <c r="O8" s="58"/>
-      <c r="P8" s="58"/>
-      <c r="Q8" s="58"/>
-      <c r="R8" s="59"/>
-      <c r="S8" s="55"/>
-      <c r="T8" s="56"/>
-      <c r="U8" s="58"/>
-      <c r="V8" s="58"/>
-      <c r="W8" s="58"/>
-      <c r="X8" s="57"/>
-      <c r="Y8" s="55"/>
-      <c r="Z8" s="58"/>
-      <c r="AA8" s="58"/>
-      <c r="AB8" s="58"/>
-      <c r="AC8" s="58"/>
-      <c r="AD8" s="59"/>
-      <c r="AE8" s="55"/>
-      <c r="AF8" s="58"/>
-      <c r="AG8" s="58"/>
-      <c r="AH8" s="58"/>
-      <c r="AI8" s="58"/>
-      <c r="AJ8" s="59"/>
-      <c r="AK8" s="55"/>
-      <c r="AL8" s="58"/>
-      <c r="AM8" s="58"/>
-      <c r="AN8" s="56"/>
-      <c r="AO8" s="58"/>
-      <c r="AP8" s="59"/>
-      <c r="AQ8" s="52"/>
-      <c r="AR8" s="52"/>
-      <c r="AS8" s="52"/>
-      <c r="AT8" s="52"/>
-      <c r="AU8" s="52"/>
-      <c r="AV8" s="52"/>
-      <c r="AW8" s="52"/>
-      <c r="AX8" s="52"/>
-      <c r="AY8" s="52"/>
-      <c r="AZ8" s="52"/>
-      <c r="BA8" s="52"/>
-      <c r="BB8" s="52"/>
+      <c r="G8" s="51"/>
+      <c r="H8" s="54"/>
+      <c r="I8" s="54"/>
+      <c r="J8" s="54"/>
+      <c r="K8" s="54"/>
+      <c r="L8" s="55"/>
+      <c r="M8" s="51"/>
+      <c r="N8" s="54"/>
+      <c r="O8" s="54"/>
+      <c r="P8" s="54"/>
+      <c r="Q8" s="54"/>
+      <c r="R8" s="55"/>
+      <c r="S8" s="51"/>
+      <c r="T8" s="52"/>
+      <c r="U8" s="54"/>
+      <c r="V8" s="54"/>
+      <c r="W8" s="54"/>
+      <c r="X8" s="53"/>
+      <c r="Y8" s="51"/>
+      <c r="Z8" s="54"/>
+      <c r="AA8" s="54"/>
+      <c r="AB8" s="54"/>
+      <c r="AC8" s="54"/>
+      <c r="AD8" s="55"/>
+      <c r="AE8" s="51"/>
+      <c r="AF8" s="54"/>
+      <c r="AG8" s="54"/>
+      <c r="AH8" s="54"/>
+      <c r="AI8" s="54"/>
+      <c r="AJ8" s="55"/>
+      <c r="AK8" s="51"/>
+      <c r="AL8" s="54"/>
+      <c r="AM8" s="54"/>
+      <c r="AN8" s="52"/>
+      <c r="AO8" s="54"/>
+      <c r="AP8" s="55"/>
+      <c r="AQ8" s="48"/>
+      <c r="AR8" s="48"/>
+      <c r="AS8" s="48"/>
+      <c r="AT8" s="48"/>
+      <c r="AU8" s="48"/>
+      <c r="AV8" s="48"/>
+      <c r="AW8" s="48"/>
+      <c r="AX8" s="48"/>
+      <c r="AY8" s="48"/>
+      <c r="AZ8" s="48"/>
+      <c r="BA8" s="48"/>
+      <c r="BB8" s="48"/>
     </row>
     <row r="9" spans="1:54" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="60">
+      <c r="A9" s="56">
         <v>7</v>
       </c>
-      <c r="B9" s="61">
+      <c r="B9" s="57">
         <v>1</v>
       </c>
-      <c r="C9" s="61">
+      <c r="C9" s="57">
         <v>0</v>
       </c>
-      <c r="D9" s="61">
+      <c r="D9" s="57">
         <v>1</v>
       </c>
-      <c r="E9" s="61">
+      <c r="E9" s="57">
         <v>0</v>
       </c>
-      <c r="F9" s="61">
+      <c r="F9" s="57">
         <v>1</v>
       </c>
-      <c r="G9" s="55"/>
-      <c r="H9" s="58"/>
-      <c r="I9" s="56"/>
-      <c r="J9" s="58"/>
-      <c r="K9" s="56"/>
-      <c r="L9" s="59"/>
-      <c r="M9" s="55"/>
-      <c r="N9" s="58"/>
-      <c r="O9" s="58"/>
-      <c r="P9" s="58"/>
-      <c r="Q9" s="58"/>
-      <c r="R9" s="59"/>
-      <c r="S9" s="55"/>
-      <c r="T9" s="58"/>
-      <c r="U9" s="56"/>
-      <c r="V9" s="58"/>
-      <c r="W9" s="56"/>
-      <c r="X9" s="59"/>
-      <c r="Y9" s="55"/>
-      <c r="Z9" s="56"/>
-      <c r="AA9" s="58"/>
-      <c r="AB9" s="58"/>
-      <c r="AC9" s="58"/>
-      <c r="AD9" s="57"/>
-      <c r="AE9" s="55"/>
-      <c r="AF9" s="58"/>
-      <c r="AG9" s="58"/>
-      <c r="AH9" s="56"/>
-      <c r="AI9" s="58"/>
-      <c r="AJ9" s="59"/>
-      <c r="AK9" s="55"/>
-      <c r="AL9" s="58"/>
-      <c r="AM9" s="56"/>
-      <c r="AN9" s="58"/>
-      <c r="AO9" s="56"/>
-      <c r="AP9" s="59"/>
-      <c r="AQ9" s="52"/>
-      <c r="AR9" s="52"/>
-      <c r="AS9" s="52"/>
-      <c r="AT9" s="52"/>
-      <c r="AU9" s="52"/>
-      <c r="AV9" s="52"/>
-      <c r="AW9" s="52"/>
-      <c r="AX9" s="52"/>
-      <c r="AY9" s="52"/>
-      <c r="AZ9" s="52"/>
-      <c r="BA9" s="52"/>
-      <c r="BB9" s="52"/>
+      <c r="G9" s="51"/>
+      <c r="H9" s="54"/>
+      <c r="I9" s="52"/>
+      <c r="J9" s="54"/>
+      <c r="K9" s="52"/>
+      <c r="L9" s="55"/>
+      <c r="M9" s="51"/>
+      <c r="N9" s="54"/>
+      <c r="O9" s="54"/>
+      <c r="P9" s="54"/>
+      <c r="Q9" s="54"/>
+      <c r="R9" s="55"/>
+      <c r="S9" s="51"/>
+      <c r="T9" s="54"/>
+      <c r="U9" s="52"/>
+      <c r="V9" s="54"/>
+      <c r="W9" s="52"/>
+      <c r="X9" s="55"/>
+      <c r="Y9" s="51"/>
+      <c r="Z9" s="52"/>
+      <c r="AA9" s="54"/>
+      <c r="AB9" s="54"/>
+      <c r="AC9" s="54"/>
+      <c r="AD9" s="53"/>
+      <c r="AE9" s="51"/>
+      <c r="AF9" s="54"/>
+      <c r="AG9" s="54"/>
+      <c r="AH9" s="52"/>
+      <c r="AI9" s="54"/>
+      <c r="AJ9" s="55"/>
+      <c r="AK9" s="51"/>
+      <c r="AL9" s="54"/>
+      <c r="AM9" s="52"/>
+      <c r="AN9" s="54"/>
+      <c r="AO9" s="52"/>
+      <c r="AP9" s="55"/>
+      <c r="AQ9" s="48"/>
+      <c r="AR9" s="48"/>
+      <c r="AS9" s="48"/>
+      <c r="AT9" s="48"/>
+      <c r="AU9" s="48"/>
+      <c r="AV9" s="48"/>
+      <c r="AW9" s="48"/>
+      <c r="AX9" s="48"/>
+      <c r="AY9" s="48"/>
+      <c r="AZ9" s="48"/>
+      <c r="BA9" s="48"/>
+      <c r="BB9" s="48"/>
     </row>
     <row r="10" spans="1:54" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="60">
+      <c r="A10" s="56">
         <v>8</v>
       </c>
-      <c r="B10" s="61">
+      <c r="B10" s="57">
         <v>2</v>
       </c>
-      <c r="C10" s="61">
+      <c r="C10" s="57">
         <v>1</v>
       </c>
-      <c r="D10" s="61">
+      <c r="D10" s="57">
         <v>2</v>
       </c>
-      <c r="E10" s="61">
+      <c r="E10" s="57">
         <v>1</v>
       </c>
-      <c r="F10" s="61">
+      <c r="F10" s="57">
         <v>2</v>
       </c>
-      <c r="G10" s="55"/>
-      <c r="H10" s="56"/>
-      <c r="I10" s="58"/>
-      <c r="J10" s="56"/>
-      <c r="K10" s="58"/>
-      <c r="L10" s="57"/>
-      <c r="M10" s="55"/>
-      <c r="N10" s="58"/>
-      <c r="O10" s="56"/>
-      <c r="P10" s="58"/>
-      <c r="Q10" s="56"/>
-      <c r="R10" s="59"/>
-      <c r="S10" s="55"/>
-      <c r="T10" s="58"/>
-      <c r="U10" s="58"/>
-      <c r="V10" s="56"/>
-      <c r="W10" s="58"/>
-      <c r="X10" s="59"/>
-      <c r="Y10" s="55"/>
-      <c r="Z10" s="58"/>
-      <c r="AA10" s="56"/>
-      <c r="AB10" s="58"/>
-      <c r="AC10" s="56"/>
-      <c r="AD10" s="59"/>
-      <c r="AE10" s="55"/>
-      <c r="AF10" s="58"/>
-      <c r="AG10" s="56"/>
-      <c r="AH10" s="58"/>
-      <c r="AI10" s="56"/>
-      <c r="AJ10" s="59"/>
-      <c r="AK10" s="55"/>
-      <c r="AL10" s="56"/>
-      <c r="AM10" s="58"/>
-      <c r="AN10" s="58"/>
-      <c r="AO10" s="58"/>
-      <c r="AP10" s="57"/>
-      <c r="AQ10" s="52"/>
-      <c r="AR10" s="52"/>
-      <c r="AS10" s="52"/>
-      <c r="AT10" s="52"/>
-      <c r="AU10" s="52"/>
-      <c r="AV10" s="52"/>
-      <c r="AW10" s="52"/>
-      <c r="AX10" s="52"/>
-      <c r="AY10" s="52"/>
-      <c r="AZ10" s="52"/>
-      <c r="BA10" s="52"/>
-      <c r="BB10" s="52"/>
+      <c r="G10" s="51"/>
+      <c r="H10" s="52"/>
+      <c r="I10" s="54"/>
+      <c r="J10" s="52"/>
+      <c r="K10" s="54"/>
+      <c r="L10" s="53"/>
+      <c r="M10" s="51"/>
+      <c r="N10" s="54"/>
+      <c r="O10" s="52"/>
+      <c r="P10" s="54"/>
+      <c r="Q10" s="52"/>
+      <c r="R10" s="55"/>
+      <c r="S10" s="51"/>
+      <c r="T10" s="54"/>
+      <c r="U10" s="54"/>
+      <c r="V10" s="52"/>
+      <c r="W10" s="54"/>
+      <c r="X10" s="55"/>
+      <c r="Y10" s="51"/>
+      <c r="Z10" s="54"/>
+      <c r="AA10" s="52"/>
+      <c r="AB10" s="54"/>
+      <c r="AC10" s="52"/>
+      <c r="AD10" s="55"/>
+      <c r="AE10" s="51"/>
+      <c r="AF10" s="54"/>
+      <c r="AG10" s="52"/>
+      <c r="AH10" s="54"/>
+      <c r="AI10" s="52"/>
+      <c r="AJ10" s="55"/>
+      <c r="AK10" s="51"/>
+      <c r="AL10" s="52"/>
+      <c r="AM10" s="54"/>
+      <c r="AN10" s="54"/>
+      <c r="AO10" s="54"/>
+      <c r="AP10" s="53"/>
+      <c r="AQ10" s="48"/>
+      <c r="AR10" s="48"/>
+      <c r="AS10" s="48"/>
+      <c r="AT10" s="48"/>
+      <c r="AU10" s="48"/>
+      <c r="AV10" s="48"/>
+      <c r="AW10" s="48"/>
+      <c r="AX10" s="48"/>
+      <c r="AY10" s="48"/>
+      <c r="AZ10" s="48"/>
+      <c r="BA10" s="48"/>
+      <c r="BB10" s="48"/>
     </row>
     <row r="11" spans="1:54" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="60">
+      <c r="A11" s="56">
         <v>9</v>
       </c>
-      <c r="B11" s="61">
+      <c r="B11" s="57">
         <v>3</v>
       </c>
-      <c r="C11" s="61">
+      <c r="C11" s="57">
         <v>2</v>
       </c>
-      <c r="D11" s="61">
+      <c r="D11" s="57">
         <v>3</v>
       </c>
-      <c r="E11" s="61">
+      <c r="E11" s="57">
         <v>2</v>
       </c>
-      <c r="F11" s="61">
+      <c r="F11" s="57">
         <v>3</v>
       </c>
-      <c r="G11" s="55"/>
-      <c r="H11" s="58"/>
-      <c r="I11" s="58"/>
-      <c r="J11" s="58"/>
-      <c r="K11" s="58"/>
-      <c r="L11" s="59"/>
-      <c r="M11" s="55"/>
-      <c r="N11" s="56"/>
-      <c r="O11" s="58"/>
-      <c r="P11" s="56"/>
-      <c r="Q11" s="58"/>
-      <c r="R11" s="57"/>
-      <c r="S11" s="55"/>
-      <c r="T11" s="58"/>
-      <c r="U11" s="58"/>
-      <c r="V11" s="58"/>
-      <c r="W11" s="58"/>
-      <c r="X11" s="59"/>
-      <c r="Y11" s="55"/>
-      <c r="Z11" s="58"/>
-      <c r="AA11" s="58"/>
-      <c r="AB11" s="56"/>
-      <c r="AC11" s="58"/>
-      <c r="AD11" s="59"/>
-      <c r="AE11" s="55"/>
-      <c r="AF11" s="56"/>
-      <c r="AG11" s="58"/>
-      <c r="AH11" s="58"/>
-      <c r="AI11" s="58"/>
-      <c r="AJ11" s="57"/>
-      <c r="AK11" s="55"/>
-      <c r="AL11" s="58"/>
-      <c r="AM11" s="58"/>
-      <c r="AN11" s="58"/>
-      <c r="AO11" s="58"/>
-      <c r="AP11" s="59"/>
-      <c r="AQ11" s="52"/>
-      <c r="AR11" s="52"/>
-      <c r="AS11" s="52"/>
-      <c r="AT11" s="52"/>
-      <c r="AU11" s="52"/>
-      <c r="AV11" s="52"/>
-      <c r="AW11" s="52"/>
-      <c r="AX11" s="52"/>
-      <c r="AY11" s="52"/>
-      <c r="AZ11" s="52"/>
-      <c r="BA11" s="52"/>
-      <c r="BB11" s="52"/>
+      <c r="G11" s="51"/>
+      <c r="H11" s="54"/>
+      <c r="I11" s="54"/>
+      <c r="J11" s="54"/>
+      <c r="K11" s="54"/>
+      <c r="L11" s="55"/>
+      <c r="M11" s="51"/>
+      <c r="N11" s="52"/>
+      <c r="O11" s="54"/>
+      <c r="P11" s="52"/>
+      <c r="Q11" s="54"/>
+      <c r="R11" s="53"/>
+      <c r="S11" s="51"/>
+      <c r="T11" s="54"/>
+      <c r="U11" s="54"/>
+      <c r="V11" s="54"/>
+      <c r="W11" s="54"/>
+      <c r="X11" s="55"/>
+      <c r="Y11" s="51"/>
+      <c r="Z11" s="54"/>
+      <c r="AA11" s="54"/>
+      <c r="AB11" s="52"/>
+      <c r="AC11" s="54"/>
+      <c r="AD11" s="55"/>
+      <c r="AE11" s="51"/>
+      <c r="AF11" s="52"/>
+      <c r="AG11" s="54"/>
+      <c r="AH11" s="54"/>
+      <c r="AI11" s="54"/>
+      <c r="AJ11" s="53"/>
+      <c r="AK11" s="51"/>
+      <c r="AL11" s="54"/>
+      <c r="AM11" s="54"/>
+      <c r="AN11" s="54"/>
+      <c r="AO11" s="54"/>
+      <c r="AP11" s="55"/>
+      <c r="AQ11" s="48"/>
+      <c r="AR11" s="48"/>
+      <c r="AS11" s="48"/>
+      <c r="AT11" s="48"/>
+      <c r="AU11" s="48"/>
+      <c r="AV11" s="48"/>
+      <c r="AW11" s="48"/>
+      <c r="AX11" s="48"/>
+      <c r="AY11" s="48"/>
+      <c r="AZ11" s="48"/>
+      <c r="BA11" s="48"/>
+      <c r="BB11" s="48"/>
     </row>
     <row r="12" spans="1:54" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="60">
+      <c r="A12" s="56">
         <v>10</v>
       </c>
-      <c r="B12" s="61">
+      <c r="B12" s="57">
         <v>0</v>
       </c>
-      <c r="C12" s="61">
+      <c r="C12" s="57">
         <v>1</v>
       </c>
-      <c r="D12" s="61">
+      <c r="D12" s="57">
         <v>2</v>
       </c>
-      <c r="E12" s="61">
+      <c r="E12" s="57">
         <v>1</v>
       </c>
-      <c r="F12" s="61">
+      <c r="F12" s="57">
         <v>0</v>
       </c>
-      <c r="G12" s="55"/>
+      <c r="G12" s="51"/>
       <c r="H12" s="63">
         <v>9</v>
       </c>
@@ -29061,7 +28719,7 @@
       <c r="J12" s="64"/>
       <c r="K12" s="64"/>
       <c r="L12" s="65"/>
-      <c r="M12" s="55"/>
+      <c r="M12" s="51"/>
       <c r="N12" s="63">
         <v>10</v>
       </c>
@@ -29069,7 +28727,7 @@
       <c r="P12" s="64"/>
       <c r="Q12" s="64"/>
       <c r="R12" s="65"/>
-      <c r="S12" s="55"/>
+      <c r="S12" s="51"/>
       <c r="T12" s="63">
         <v>11</v>
       </c>
@@ -29077,7 +28735,7 @@
       <c r="V12" s="64"/>
       <c r="W12" s="64"/>
       <c r="X12" s="65"/>
-      <c r="Y12" s="55"/>
+      <c r="Y12" s="51"/>
       <c r="Z12" s="63">
         <v>12</v>
       </c>
@@ -29085,7 +28743,7 @@
       <c r="AB12" s="64"/>
       <c r="AC12" s="64"/>
       <c r="AD12" s="65"/>
-      <c r="AE12" s="55"/>
+      <c r="AE12" s="51"/>
       <c r="AF12" s="63">
         <v>13</v>
       </c>
@@ -29093,7 +28751,7 @@
       <c r="AH12" s="64"/>
       <c r="AI12" s="64"/>
       <c r="AJ12" s="65"/>
-      <c r="AK12" s="55"/>
+      <c r="AK12" s="51"/>
       <c r="AL12" s="63">
         <v>14</v>
       </c>
@@ -29101,950 +28759,950 @@
       <c r="AN12" s="64"/>
       <c r="AO12" s="64"/>
       <c r="AP12" s="65"/>
-      <c r="AQ12" s="52"/>
-      <c r="AR12" s="52"/>
-      <c r="AS12" s="52"/>
-      <c r="AT12" s="52"/>
-      <c r="AU12" s="52"/>
-      <c r="AV12" s="52"/>
-      <c r="AW12" s="52"/>
-      <c r="AX12" s="52"/>
-      <c r="AY12" s="52"/>
-      <c r="AZ12" s="52"/>
-      <c r="BA12" s="52"/>
-      <c r="BB12" s="52"/>
+      <c r="AQ12" s="48"/>
+      <c r="AR12" s="48"/>
+      <c r="AS12" s="48"/>
+      <c r="AT12" s="48"/>
+      <c r="AU12" s="48"/>
+      <c r="AV12" s="48"/>
+      <c r="AW12" s="48"/>
+      <c r="AX12" s="48"/>
+      <c r="AY12" s="48"/>
+      <c r="AZ12" s="48"/>
+      <c r="BA12" s="48"/>
+      <c r="BB12" s="48"/>
     </row>
     <row r="13" spans="1:54" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="60">
+      <c r="A13" s="56">
         <v>11</v>
       </c>
-      <c r="B13" s="61">
+      <c r="B13" s="57">
         <v>1</v>
       </c>
-      <c r="C13" s="61">
+      <c r="C13" s="57">
         <v>2</v>
       </c>
-      <c r="D13" s="61">
+      <c r="D13" s="57">
         <v>3</v>
       </c>
-      <c r="E13" s="61">
+      <c r="E13" s="57">
         <v>2</v>
       </c>
-      <c r="F13" s="61">
+      <c r="F13" s="57">
         <v>1</v>
       </c>
-      <c r="G13" s="52"/>
-      <c r="H13" s="52"/>
-      <c r="I13" s="52"/>
-      <c r="J13" s="52"/>
-      <c r="K13" s="52"/>
-      <c r="L13" s="52"/>
-      <c r="M13" s="52"/>
-      <c r="N13" s="52"/>
-      <c r="O13" s="52"/>
-      <c r="P13" s="52"/>
-      <c r="Q13" s="52"/>
-      <c r="R13" s="52"/>
-      <c r="S13" s="52"/>
-      <c r="T13" s="52"/>
-      <c r="U13" s="52"/>
-      <c r="V13" s="52"/>
-      <c r="W13" s="52"/>
-      <c r="X13" s="52"/>
-      <c r="Y13" s="52"/>
-      <c r="Z13" s="52"/>
-      <c r="AA13" s="52"/>
-      <c r="AB13" s="52"/>
-      <c r="AC13" s="52"/>
-      <c r="AD13" s="52"/>
-      <c r="AE13" s="52"/>
-      <c r="AF13" s="52"/>
-      <c r="AG13" s="52"/>
-      <c r="AH13" s="52"/>
-      <c r="AI13" s="52"/>
-      <c r="AJ13" s="52"/>
-      <c r="AK13" s="52"/>
-      <c r="AL13" s="52"/>
-      <c r="AM13" s="52"/>
-      <c r="AN13" s="52"/>
-      <c r="AO13" s="52"/>
-      <c r="AP13" s="52"/>
-      <c r="AQ13" s="52"/>
-      <c r="AR13" s="52"/>
-      <c r="AS13" s="52"/>
-      <c r="AT13" s="52"/>
-      <c r="AU13" s="52"/>
-      <c r="AV13" s="52"/>
-      <c r="AW13" s="52"/>
-      <c r="AX13" s="52"/>
-      <c r="AY13" s="52"/>
-      <c r="AZ13" s="52"/>
-      <c r="BA13" s="52"/>
-      <c r="BB13" s="52"/>
+      <c r="G13" s="48"/>
+      <c r="H13" s="48"/>
+      <c r="I13" s="48"/>
+      <c r="J13" s="48"/>
+      <c r="K13" s="48"/>
+      <c r="L13" s="48"/>
+      <c r="M13" s="48"/>
+      <c r="N13" s="48"/>
+      <c r="O13" s="48"/>
+      <c r="P13" s="48"/>
+      <c r="Q13" s="48"/>
+      <c r="R13" s="48"/>
+      <c r="S13" s="48"/>
+      <c r="T13" s="48"/>
+      <c r="U13" s="48"/>
+      <c r="V13" s="48"/>
+      <c r="W13" s="48"/>
+      <c r="X13" s="48"/>
+      <c r="Y13" s="48"/>
+      <c r="Z13" s="48"/>
+      <c r="AA13" s="48"/>
+      <c r="AB13" s="48"/>
+      <c r="AC13" s="48"/>
+      <c r="AD13" s="48"/>
+      <c r="AE13" s="48"/>
+      <c r="AF13" s="48"/>
+      <c r="AG13" s="48"/>
+      <c r="AH13" s="48"/>
+      <c r="AI13" s="48"/>
+      <c r="AJ13" s="48"/>
+      <c r="AK13" s="48"/>
+      <c r="AL13" s="48"/>
+      <c r="AM13" s="48"/>
+      <c r="AN13" s="48"/>
+      <c r="AO13" s="48"/>
+      <c r="AP13" s="48"/>
+      <c r="AQ13" s="48"/>
+      <c r="AR13" s="48"/>
+      <c r="AS13" s="48"/>
+      <c r="AT13" s="48"/>
+      <c r="AU13" s="48"/>
+      <c r="AV13" s="48"/>
+      <c r="AW13" s="48"/>
+      <c r="AX13" s="48"/>
+      <c r="AY13" s="48"/>
+      <c r="AZ13" s="48"/>
+      <c r="BA13" s="48"/>
+      <c r="BB13" s="48"/>
     </row>
     <row r="14" spans="1:54" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="60">
+      <c r="A14" s="56">
         <v>12</v>
       </c>
-      <c r="B14" s="61">
+      <c r="B14" s="57">
         <v>3</v>
       </c>
-      <c r="C14" s="61">
+      <c r="C14" s="57">
         <v>2</v>
       </c>
-      <c r="D14" s="61">
+      <c r="D14" s="57">
         <v>1</v>
       </c>
-      <c r="E14" s="61">
+      <c r="E14" s="57">
         <v>2</v>
       </c>
-      <c r="F14" s="61">
+      <c r="F14" s="57">
         <v>3</v>
       </c>
-      <c r="G14" s="52"/>
-      <c r="H14" s="52"/>
-      <c r="I14" s="52"/>
-      <c r="J14" s="52"/>
-      <c r="K14" s="52"/>
-      <c r="L14" s="52"/>
-      <c r="M14" s="52"/>
-      <c r="N14" s="52"/>
-      <c r="O14" s="52"/>
-      <c r="P14" s="52"/>
-      <c r="Q14" s="52"/>
-      <c r="R14" s="52"/>
-      <c r="S14" s="52"/>
-      <c r="T14" s="52"/>
-      <c r="U14" s="52"/>
-      <c r="V14" s="52"/>
-      <c r="W14" s="52"/>
-      <c r="X14" s="52"/>
-      <c r="Y14" s="52"/>
-      <c r="Z14" s="52"/>
-      <c r="AA14" s="52"/>
-      <c r="AB14" s="52"/>
-      <c r="AC14" s="52"/>
-      <c r="AD14" s="52"/>
-      <c r="AE14" s="52"/>
-      <c r="AF14" s="52"/>
-      <c r="AG14" s="52"/>
-      <c r="AH14" s="52"/>
-      <c r="AI14" s="52"/>
-      <c r="AJ14" s="52"/>
-      <c r="AK14" s="52"/>
-      <c r="AL14" s="52"/>
-      <c r="AM14" s="52"/>
-      <c r="AN14" s="52"/>
-      <c r="AO14" s="52"/>
-      <c r="AP14" s="52"/>
-      <c r="AQ14" s="52"/>
-      <c r="AR14" s="52"/>
-      <c r="AS14" s="52"/>
-      <c r="AT14" s="52"/>
-      <c r="AU14" s="52"/>
-      <c r="AV14" s="52"/>
-      <c r="AW14" s="52"/>
-      <c r="AX14" s="52"/>
-      <c r="AY14" s="52"/>
-      <c r="AZ14" s="52"/>
-      <c r="BA14" s="52"/>
-      <c r="BB14" s="52"/>
+      <c r="G14" s="48"/>
+      <c r="H14" s="48"/>
+      <c r="I14" s="48"/>
+      <c r="J14" s="48"/>
+      <c r="K14" s="48"/>
+      <c r="L14" s="48"/>
+      <c r="M14" s="48"/>
+      <c r="N14" s="48"/>
+      <c r="O14" s="48"/>
+      <c r="P14" s="48"/>
+      <c r="Q14" s="48"/>
+      <c r="R14" s="48"/>
+      <c r="S14" s="48"/>
+      <c r="T14" s="48"/>
+      <c r="U14" s="48"/>
+      <c r="V14" s="48"/>
+      <c r="W14" s="48"/>
+      <c r="X14" s="48"/>
+      <c r="Y14" s="48"/>
+      <c r="Z14" s="48"/>
+      <c r="AA14" s="48"/>
+      <c r="AB14" s="48"/>
+      <c r="AC14" s="48"/>
+      <c r="AD14" s="48"/>
+      <c r="AE14" s="48"/>
+      <c r="AF14" s="48"/>
+      <c r="AG14" s="48"/>
+      <c r="AH14" s="48"/>
+      <c r="AI14" s="48"/>
+      <c r="AJ14" s="48"/>
+      <c r="AK14" s="48"/>
+      <c r="AL14" s="48"/>
+      <c r="AM14" s="48"/>
+      <c r="AN14" s="48"/>
+      <c r="AO14" s="48"/>
+      <c r="AP14" s="48"/>
+      <c r="AQ14" s="48"/>
+      <c r="AR14" s="48"/>
+      <c r="AS14" s="48"/>
+      <c r="AT14" s="48"/>
+      <c r="AU14" s="48"/>
+      <c r="AV14" s="48"/>
+      <c r="AW14" s="48"/>
+      <c r="AX14" s="48"/>
+      <c r="AY14" s="48"/>
+      <c r="AZ14" s="48"/>
+      <c r="BA14" s="48"/>
+      <c r="BB14" s="48"/>
     </row>
     <row r="15" spans="1:54" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="60">
+      <c r="A15" s="56">
         <v>13</v>
       </c>
-      <c r="B15" s="61">
+      <c r="B15" s="57">
         <v>2</v>
       </c>
-      <c r="C15" s="61">
+      <c r="C15" s="57">
         <v>1</v>
       </c>
-      <c r="D15" s="61">
+      <c r="D15" s="57">
         <v>0</v>
       </c>
-      <c r="E15" s="61">
+      <c r="E15" s="57">
         <v>1</v>
       </c>
-      <c r="F15" s="61">
+      <c r="F15" s="57">
         <v>2</v>
       </c>
-      <c r="G15" s="52"/>
-      <c r="H15" s="52"/>
-      <c r="I15" s="52"/>
-      <c r="J15" s="52"/>
-      <c r="K15" s="52"/>
-      <c r="L15" s="52"/>
-      <c r="M15" s="52"/>
-      <c r="N15" s="52"/>
-      <c r="O15" s="52"/>
-      <c r="P15" s="52"/>
-      <c r="Q15" s="52"/>
-      <c r="R15" s="52"/>
-      <c r="S15" s="52"/>
-      <c r="T15" s="52"/>
-      <c r="U15" s="52"/>
-      <c r="V15" s="52"/>
-      <c r="W15" s="52"/>
-      <c r="X15" s="52"/>
-      <c r="Y15" s="52"/>
-      <c r="Z15" s="52"/>
-      <c r="AA15" s="52"/>
-      <c r="AB15" s="52"/>
-      <c r="AC15" s="52"/>
-      <c r="AD15" s="52"/>
-      <c r="AE15" s="52"/>
-      <c r="AF15" s="52"/>
-      <c r="AG15" s="52"/>
-      <c r="AH15" s="52"/>
-      <c r="AI15" s="52"/>
-      <c r="AJ15" s="52"/>
-      <c r="AK15" s="52"/>
-      <c r="AL15" s="52"/>
-      <c r="AM15" s="52"/>
-      <c r="AN15" s="52"/>
-      <c r="AO15" s="52"/>
-      <c r="AP15" s="52"/>
-      <c r="AQ15" s="52"/>
-      <c r="AR15" s="52"/>
-      <c r="AS15" s="52"/>
-      <c r="AT15" s="52"/>
-      <c r="AU15" s="52"/>
-      <c r="AV15" s="52"/>
-      <c r="AW15" s="52"/>
-      <c r="AX15" s="52"/>
-      <c r="AY15" s="52"/>
-      <c r="AZ15" s="52"/>
-      <c r="BA15" s="52"/>
-      <c r="BB15" s="52"/>
+      <c r="G15" s="48"/>
+      <c r="H15" s="48"/>
+      <c r="I15" s="48"/>
+      <c r="J15" s="48"/>
+      <c r="K15" s="48"/>
+      <c r="L15" s="48"/>
+      <c r="M15" s="48"/>
+      <c r="N15" s="48"/>
+      <c r="O15" s="48"/>
+      <c r="P15" s="48"/>
+      <c r="Q15" s="48"/>
+      <c r="R15" s="48"/>
+      <c r="S15" s="48"/>
+      <c r="T15" s="48"/>
+      <c r="U15" s="48"/>
+      <c r="V15" s="48"/>
+      <c r="W15" s="48"/>
+      <c r="X15" s="48"/>
+      <c r="Y15" s="48"/>
+      <c r="Z15" s="48"/>
+      <c r="AA15" s="48"/>
+      <c r="AB15" s="48"/>
+      <c r="AC15" s="48"/>
+      <c r="AD15" s="48"/>
+      <c r="AE15" s="48"/>
+      <c r="AF15" s="48"/>
+      <c r="AG15" s="48"/>
+      <c r="AH15" s="48"/>
+      <c r="AI15" s="48"/>
+      <c r="AJ15" s="48"/>
+      <c r="AK15" s="48"/>
+      <c r="AL15" s="48"/>
+      <c r="AM15" s="48"/>
+      <c r="AN15" s="48"/>
+      <c r="AO15" s="48"/>
+      <c r="AP15" s="48"/>
+      <c r="AQ15" s="48"/>
+      <c r="AR15" s="48"/>
+      <c r="AS15" s="48"/>
+      <c r="AT15" s="48"/>
+      <c r="AU15" s="48"/>
+      <c r="AV15" s="48"/>
+      <c r="AW15" s="48"/>
+      <c r="AX15" s="48"/>
+      <c r="AY15" s="48"/>
+      <c r="AZ15" s="48"/>
+      <c r="BA15" s="48"/>
+      <c r="BB15" s="48"/>
     </row>
     <row r="16" spans="1:54" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="62"/>
-      <c r="B16" s="62"/>
-      <c r="C16" s="62"/>
-      <c r="D16" s="62"/>
-      <c r="E16" s="62"/>
-      <c r="F16" s="62"/>
-      <c r="G16" s="62"/>
-      <c r="H16" s="62"/>
-      <c r="I16" s="62"/>
-      <c r="J16" s="62"/>
-      <c r="K16" s="62"/>
-      <c r="L16" s="62"/>
-      <c r="M16" s="62"/>
-      <c r="N16" s="62"/>
-      <c r="O16" s="62"/>
-      <c r="P16" s="62"/>
-      <c r="Q16" s="62"/>
-      <c r="R16" s="62"/>
-      <c r="S16" s="62"/>
-      <c r="T16" s="62"/>
-      <c r="U16" s="62"/>
-      <c r="V16" s="62"/>
-      <c r="W16" s="62"/>
-      <c r="X16" s="62"/>
-      <c r="Y16" s="62"/>
-      <c r="Z16" s="62"/>
-      <c r="AA16" s="62"/>
-      <c r="AB16" s="62"/>
-      <c r="AC16" s="62"/>
-      <c r="AD16" s="62"/>
-      <c r="AE16" s="62"/>
-      <c r="AF16" s="62"/>
-      <c r="AG16" s="62"/>
-      <c r="AH16" s="62"/>
-      <c r="AI16" s="62"/>
-      <c r="AJ16" s="62"/>
-      <c r="AK16" s="62"/>
-      <c r="AL16" s="62"/>
-      <c r="AM16" s="62"/>
-      <c r="AN16" s="62"/>
-      <c r="AO16" s="62"/>
-      <c r="AP16" s="62"/>
-      <c r="AQ16" s="62"/>
-      <c r="AR16" s="62"/>
-      <c r="AS16" s="62"/>
-      <c r="AT16" s="62"/>
-      <c r="AU16" s="62"/>
-      <c r="AV16" s="62"/>
-      <c r="AW16" s="62"/>
-      <c r="AX16" s="62"/>
-      <c r="AY16" s="62"/>
-      <c r="AZ16" s="62"/>
-      <c r="BA16" s="62"/>
-      <c r="BB16" s="62"/>
+      <c r="A16" s="58"/>
+      <c r="B16" s="58"/>
+      <c r="C16" s="58"/>
+      <c r="D16" s="58"/>
+      <c r="E16" s="58"/>
+      <c r="F16" s="58"/>
+      <c r="G16" s="58"/>
+      <c r="H16" s="58"/>
+      <c r="I16" s="58"/>
+      <c r="J16" s="58"/>
+      <c r="K16" s="58"/>
+      <c r="L16" s="58"/>
+      <c r="M16" s="58"/>
+      <c r="N16" s="58"/>
+      <c r="O16" s="58"/>
+      <c r="P16" s="58"/>
+      <c r="Q16" s="58"/>
+      <c r="R16" s="58"/>
+      <c r="S16" s="58"/>
+      <c r="T16" s="58"/>
+      <c r="U16" s="58"/>
+      <c r="V16" s="58"/>
+      <c r="W16" s="58"/>
+      <c r="X16" s="58"/>
+      <c r="Y16" s="58"/>
+      <c r="Z16" s="58"/>
+      <c r="AA16" s="58"/>
+      <c r="AB16" s="58"/>
+      <c r="AC16" s="58"/>
+      <c r="AD16" s="58"/>
+      <c r="AE16" s="58"/>
+      <c r="AF16" s="58"/>
+      <c r="AG16" s="58"/>
+      <c r="AH16" s="58"/>
+      <c r="AI16" s="58"/>
+      <c r="AJ16" s="58"/>
+      <c r="AK16" s="58"/>
+      <c r="AL16" s="58"/>
+      <c r="AM16" s="58"/>
+      <c r="AN16" s="58"/>
+      <c r="AO16" s="58"/>
+      <c r="AP16" s="58"/>
+      <c r="AQ16" s="58"/>
+      <c r="AR16" s="58"/>
+      <c r="AS16" s="58"/>
+      <c r="AT16" s="58"/>
+      <c r="AU16" s="58"/>
+      <c r="AV16" s="58"/>
+      <c r="AW16" s="58"/>
+      <c r="AX16" s="58"/>
+      <c r="AY16" s="58"/>
+      <c r="AZ16" s="58"/>
+      <c r="BA16" s="58"/>
+      <c r="BB16" s="58"/>
     </row>
     <row r="17" spans="1:54" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="62"/>
-      <c r="B17" s="62"/>
-      <c r="C17" s="62"/>
-      <c r="D17" s="62"/>
-      <c r="E17" s="62"/>
-      <c r="F17" s="62"/>
-      <c r="G17" s="62"/>
-      <c r="H17" s="62"/>
-      <c r="I17" s="62"/>
-      <c r="J17" s="62"/>
-      <c r="K17" s="62"/>
-      <c r="L17" s="62"/>
-      <c r="M17" s="62"/>
-      <c r="N17" s="62"/>
-      <c r="O17" s="62"/>
-      <c r="P17" s="62"/>
-      <c r="Q17" s="62"/>
-      <c r="R17" s="62"/>
-      <c r="S17" s="62"/>
-      <c r="T17" s="62"/>
-      <c r="U17" s="62"/>
-      <c r="V17" s="62"/>
-      <c r="W17" s="62"/>
-      <c r="X17" s="62"/>
-      <c r="Y17" s="62"/>
-      <c r="Z17" s="62"/>
-      <c r="AA17" s="62"/>
-      <c r="AB17" s="62"/>
-      <c r="AC17" s="62"/>
-      <c r="AD17" s="62"/>
-      <c r="AE17" s="62"/>
-      <c r="AF17" s="62"/>
-      <c r="AG17" s="62"/>
-      <c r="AH17" s="62"/>
-      <c r="AI17" s="62"/>
-      <c r="AJ17" s="62"/>
-      <c r="AK17" s="62"/>
-      <c r="AL17" s="62"/>
-      <c r="AM17" s="62"/>
-      <c r="AN17" s="62"/>
-      <c r="AO17" s="62"/>
-      <c r="AP17" s="62"/>
-      <c r="AQ17" s="62"/>
-      <c r="AR17" s="62"/>
-      <c r="AS17" s="62"/>
-      <c r="AT17" s="62"/>
-      <c r="AU17" s="62"/>
-      <c r="AV17" s="62"/>
-      <c r="AW17" s="62"/>
-      <c r="AX17" s="62"/>
-      <c r="AY17" s="62"/>
-      <c r="AZ17" s="62"/>
-      <c r="BA17" s="62"/>
-      <c r="BB17" s="62"/>
+      <c r="A17" s="58"/>
+      <c r="B17" s="58"/>
+      <c r="C17" s="58"/>
+      <c r="D17" s="58"/>
+      <c r="E17" s="58"/>
+      <c r="F17" s="58"/>
+      <c r="G17" s="58"/>
+      <c r="H17" s="58"/>
+      <c r="I17" s="58"/>
+      <c r="J17" s="58"/>
+      <c r="K17" s="58"/>
+      <c r="L17" s="58"/>
+      <c r="M17" s="58"/>
+      <c r="N17" s="58"/>
+      <c r="O17" s="58"/>
+      <c r="P17" s="58"/>
+      <c r="Q17" s="58"/>
+      <c r="R17" s="58"/>
+      <c r="S17" s="58"/>
+      <c r="T17" s="58"/>
+      <c r="U17" s="58"/>
+      <c r="V17" s="58"/>
+      <c r="W17" s="58"/>
+      <c r="X17" s="58"/>
+      <c r="Y17" s="58"/>
+      <c r="Z17" s="58"/>
+      <c r="AA17" s="58"/>
+      <c r="AB17" s="58"/>
+      <c r="AC17" s="58"/>
+      <c r="AD17" s="58"/>
+      <c r="AE17" s="58"/>
+      <c r="AF17" s="58"/>
+      <c r="AG17" s="58"/>
+      <c r="AH17" s="58"/>
+      <c r="AI17" s="58"/>
+      <c r="AJ17" s="58"/>
+      <c r="AK17" s="58"/>
+      <c r="AL17" s="58"/>
+      <c r="AM17" s="58"/>
+      <c r="AN17" s="58"/>
+      <c r="AO17" s="58"/>
+      <c r="AP17" s="58"/>
+      <c r="AQ17" s="58"/>
+      <c r="AR17" s="58"/>
+      <c r="AS17" s="58"/>
+      <c r="AT17" s="58"/>
+      <c r="AU17" s="58"/>
+      <c r="AV17" s="58"/>
+      <c r="AW17" s="58"/>
+      <c r="AX17" s="58"/>
+      <c r="AY17" s="58"/>
+      <c r="AZ17" s="58"/>
+      <c r="BA17" s="58"/>
+      <c r="BB17" s="58"/>
     </row>
     <row r="18" spans="1:54" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="62"/>
-      <c r="B18" s="62"/>
-      <c r="C18" s="62"/>
-      <c r="D18" s="62"/>
-      <c r="E18" s="62"/>
-      <c r="F18" s="62"/>
-      <c r="G18" s="62"/>
-      <c r="H18" s="62"/>
-      <c r="I18" s="62"/>
-      <c r="J18" s="62"/>
-      <c r="K18" s="62"/>
-      <c r="L18" s="62"/>
-      <c r="M18" s="62"/>
-      <c r="N18" s="62"/>
-      <c r="O18" s="62"/>
-      <c r="P18" s="62"/>
-      <c r="Q18" s="62"/>
-      <c r="R18" s="62"/>
-      <c r="S18" s="62"/>
-      <c r="T18" s="62"/>
-      <c r="U18" s="62"/>
-      <c r="V18" s="62"/>
-      <c r="W18" s="62"/>
-      <c r="X18" s="62"/>
-      <c r="Y18" s="62"/>
-      <c r="Z18" s="62"/>
-      <c r="AA18" s="62"/>
-      <c r="AB18" s="62"/>
-      <c r="AC18" s="62"/>
-      <c r="AD18" s="62"/>
-      <c r="AE18" s="62"/>
-      <c r="AF18" s="62"/>
-      <c r="AG18" s="62"/>
-      <c r="AH18" s="62"/>
-      <c r="AI18" s="62"/>
-      <c r="AJ18" s="62"/>
-      <c r="AK18" s="62"/>
-      <c r="AL18" s="62"/>
-      <c r="AM18" s="62"/>
-      <c r="AN18" s="62"/>
-      <c r="AO18" s="62"/>
-      <c r="AP18" s="62"/>
-      <c r="AQ18" s="62"/>
-      <c r="AR18" s="62"/>
-      <c r="AS18" s="62"/>
-      <c r="AT18" s="62"/>
-      <c r="AU18" s="62"/>
-      <c r="AV18" s="62"/>
-      <c r="AW18" s="62"/>
-      <c r="AX18" s="62"/>
-      <c r="AY18" s="62"/>
-      <c r="AZ18" s="62"/>
-      <c r="BA18" s="62"/>
-      <c r="BB18" s="62"/>
+      <c r="A18" s="58"/>
+      <c r="B18" s="58"/>
+      <c r="C18" s="58"/>
+      <c r="D18" s="58"/>
+      <c r="E18" s="58"/>
+      <c r="F18" s="58"/>
+      <c r="G18" s="58"/>
+      <c r="H18" s="58"/>
+      <c r="I18" s="58"/>
+      <c r="J18" s="58"/>
+      <c r="K18" s="58"/>
+      <c r="L18" s="58"/>
+      <c r="M18" s="58"/>
+      <c r="N18" s="58"/>
+      <c r="O18" s="58"/>
+      <c r="P18" s="58"/>
+      <c r="Q18" s="58"/>
+      <c r="R18" s="58"/>
+      <c r="S18" s="58"/>
+      <c r="T18" s="58"/>
+      <c r="U18" s="58"/>
+      <c r="V18" s="58"/>
+      <c r="W18" s="58"/>
+      <c r="X18" s="58"/>
+      <c r="Y18" s="58"/>
+      <c r="Z18" s="58"/>
+      <c r="AA18" s="58"/>
+      <c r="AB18" s="58"/>
+      <c r="AC18" s="58"/>
+      <c r="AD18" s="58"/>
+      <c r="AE18" s="58"/>
+      <c r="AF18" s="58"/>
+      <c r="AG18" s="58"/>
+      <c r="AH18" s="58"/>
+      <c r="AI18" s="58"/>
+      <c r="AJ18" s="58"/>
+      <c r="AK18" s="58"/>
+      <c r="AL18" s="58"/>
+      <c r="AM18" s="58"/>
+      <c r="AN18" s="58"/>
+      <c r="AO18" s="58"/>
+      <c r="AP18" s="58"/>
+      <c r="AQ18" s="58"/>
+      <c r="AR18" s="58"/>
+      <c r="AS18" s="58"/>
+      <c r="AT18" s="58"/>
+      <c r="AU18" s="58"/>
+      <c r="AV18" s="58"/>
+      <c r="AW18" s="58"/>
+      <c r="AX18" s="58"/>
+      <c r="AY18" s="58"/>
+      <c r="AZ18" s="58"/>
+      <c r="BA18" s="58"/>
+      <c r="BB18" s="58"/>
     </row>
     <row r="19" spans="1:54" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="62"/>
-      <c r="B19" s="62"/>
-      <c r="C19" s="62"/>
-      <c r="D19" s="62"/>
-      <c r="E19" s="62"/>
-      <c r="F19" s="62"/>
-      <c r="G19" s="62"/>
-      <c r="H19" s="62"/>
-      <c r="I19" s="62"/>
-      <c r="J19" s="62"/>
-      <c r="K19" s="62"/>
-      <c r="L19" s="62"/>
-      <c r="M19" s="62"/>
-      <c r="N19" s="62"/>
-      <c r="O19" s="62"/>
-      <c r="P19" s="62"/>
-      <c r="Q19" s="62"/>
-      <c r="R19" s="62"/>
-      <c r="S19" s="62"/>
-      <c r="T19" s="62"/>
-      <c r="U19" s="62"/>
-      <c r="V19" s="62"/>
-      <c r="W19" s="62"/>
-      <c r="X19" s="62"/>
-      <c r="Y19" s="62"/>
-      <c r="Z19" s="62"/>
-      <c r="AA19" s="62"/>
-      <c r="AB19" s="62"/>
-      <c r="AC19" s="62"/>
-      <c r="AD19" s="62"/>
-      <c r="AE19" s="62"/>
-      <c r="AF19" s="62"/>
-      <c r="AG19" s="62"/>
-      <c r="AH19" s="62"/>
-      <c r="AI19" s="62"/>
-      <c r="AJ19" s="62"/>
-      <c r="AK19" s="62"/>
-      <c r="AL19" s="62"/>
-      <c r="AM19" s="62"/>
-      <c r="AN19" s="62"/>
-      <c r="AO19" s="62"/>
-      <c r="AP19" s="62"/>
-      <c r="AQ19" s="62"/>
-      <c r="AR19" s="62"/>
-      <c r="AS19" s="62"/>
-      <c r="AT19" s="62"/>
-      <c r="AU19" s="62"/>
-      <c r="AV19" s="62"/>
-      <c r="AW19" s="62"/>
-      <c r="AX19" s="62"/>
-      <c r="AY19" s="62"/>
-      <c r="AZ19" s="62"/>
-      <c r="BA19" s="62"/>
-      <c r="BB19" s="62"/>
+      <c r="A19" s="58"/>
+      <c r="B19" s="58"/>
+      <c r="C19" s="58"/>
+      <c r="D19" s="58"/>
+      <c r="E19" s="58"/>
+      <c r="F19" s="58"/>
+      <c r="G19" s="58"/>
+      <c r="H19" s="58"/>
+      <c r="I19" s="58"/>
+      <c r="J19" s="58"/>
+      <c r="K19" s="58"/>
+      <c r="L19" s="58"/>
+      <c r="M19" s="58"/>
+      <c r="N19" s="58"/>
+      <c r="O19" s="58"/>
+      <c r="P19" s="58"/>
+      <c r="Q19" s="58"/>
+      <c r="R19" s="58"/>
+      <c r="S19" s="58"/>
+      <c r="T19" s="58"/>
+      <c r="U19" s="58"/>
+      <c r="V19" s="58"/>
+      <c r="W19" s="58"/>
+      <c r="X19" s="58"/>
+      <c r="Y19" s="58"/>
+      <c r="Z19" s="58"/>
+      <c r="AA19" s="58"/>
+      <c r="AB19" s="58"/>
+      <c r="AC19" s="58"/>
+      <c r="AD19" s="58"/>
+      <c r="AE19" s="58"/>
+      <c r="AF19" s="58"/>
+      <c r="AG19" s="58"/>
+      <c r="AH19" s="58"/>
+      <c r="AI19" s="58"/>
+      <c r="AJ19" s="58"/>
+      <c r="AK19" s="58"/>
+      <c r="AL19" s="58"/>
+      <c r="AM19" s="58"/>
+      <c r="AN19" s="58"/>
+      <c r="AO19" s="58"/>
+      <c r="AP19" s="58"/>
+      <c r="AQ19" s="58"/>
+      <c r="AR19" s="58"/>
+      <c r="AS19" s="58"/>
+      <c r="AT19" s="58"/>
+      <c r="AU19" s="58"/>
+      <c r="AV19" s="58"/>
+      <c r="AW19" s="58"/>
+      <c r="AX19" s="58"/>
+      <c r="AY19" s="58"/>
+      <c r="AZ19" s="58"/>
+      <c r="BA19" s="58"/>
+      <c r="BB19" s="58"/>
     </row>
     <row r="20" spans="1:54" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="62"/>
-      <c r="B20" s="62"/>
-      <c r="C20" s="62"/>
-      <c r="D20" s="62"/>
-      <c r="E20" s="62"/>
-      <c r="F20" s="62"/>
-      <c r="G20" s="62"/>
-      <c r="H20" s="62"/>
-      <c r="I20" s="62"/>
-      <c r="J20" s="62"/>
-      <c r="K20" s="62"/>
-      <c r="L20" s="62"/>
-      <c r="M20" s="62"/>
-      <c r="N20" s="62"/>
-      <c r="O20" s="62"/>
-      <c r="P20" s="62"/>
-      <c r="Q20" s="62"/>
-      <c r="R20" s="62"/>
-      <c r="S20" s="62"/>
-      <c r="T20" s="62"/>
-      <c r="U20" s="62"/>
-      <c r="V20" s="62"/>
-      <c r="W20" s="62"/>
-      <c r="X20" s="62"/>
-      <c r="Y20" s="62"/>
-      <c r="Z20" s="62"/>
-      <c r="AA20" s="62"/>
-      <c r="AB20" s="62"/>
-      <c r="AC20" s="62"/>
-      <c r="AD20" s="62"/>
-      <c r="AE20" s="62"/>
-      <c r="AF20" s="62"/>
-      <c r="AG20" s="62"/>
-      <c r="AH20" s="62"/>
-      <c r="AI20" s="62"/>
-      <c r="AJ20" s="62"/>
-      <c r="AK20" s="62"/>
-      <c r="AL20" s="62"/>
-      <c r="AM20" s="62"/>
-      <c r="AN20" s="62"/>
-      <c r="AO20" s="62"/>
-      <c r="AP20" s="62"/>
-      <c r="AQ20" s="62"/>
-      <c r="AR20" s="62"/>
-      <c r="AS20" s="62"/>
-      <c r="AT20" s="62"/>
-      <c r="AU20" s="62"/>
-      <c r="AV20" s="62"/>
-      <c r="AW20" s="62"/>
-      <c r="AX20" s="62"/>
-      <c r="AY20" s="62"/>
-      <c r="AZ20" s="62"/>
-      <c r="BA20" s="62"/>
-      <c r="BB20" s="62"/>
+      <c r="A20" s="58"/>
+      <c r="B20" s="58"/>
+      <c r="C20" s="58"/>
+      <c r="D20" s="58"/>
+      <c r="E20" s="58"/>
+      <c r="F20" s="58"/>
+      <c r="G20" s="58"/>
+      <c r="H20" s="58"/>
+      <c r="I20" s="58"/>
+      <c r="J20" s="58"/>
+      <c r="K20" s="58"/>
+      <c r="L20" s="58"/>
+      <c r="M20" s="58"/>
+      <c r="N20" s="58"/>
+      <c r="O20" s="58"/>
+      <c r="P20" s="58"/>
+      <c r="Q20" s="58"/>
+      <c r="R20" s="58"/>
+      <c r="S20" s="58"/>
+      <c r="T20" s="58"/>
+      <c r="U20" s="58"/>
+      <c r="V20" s="58"/>
+      <c r="W20" s="58"/>
+      <c r="X20" s="58"/>
+      <c r="Y20" s="58"/>
+      <c r="Z20" s="58"/>
+      <c r="AA20" s="58"/>
+      <c r="AB20" s="58"/>
+      <c r="AC20" s="58"/>
+      <c r="AD20" s="58"/>
+      <c r="AE20" s="58"/>
+      <c r="AF20" s="58"/>
+      <c r="AG20" s="58"/>
+      <c r="AH20" s="58"/>
+      <c r="AI20" s="58"/>
+      <c r="AJ20" s="58"/>
+      <c r="AK20" s="58"/>
+      <c r="AL20" s="58"/>
+      <c r="AM20" s="58"/>
+      <c r="AN20" s="58"/>
+      <c r="AO20" s="58"/>
+      <c r="AP20" s="58"/>
+      <c r="AQ20" s="58"/>
+      <c r="AR20" s="58"/>
+      <c r="AS20" s="58"/>
+      <c r="AT20" s="58"/>
+      <c r="AU20" s="58"/>
+      <c r="AV20" s="58"/>
+      <c r="AW20" s="58"/>
+      <c r="AX20" s="58"/>
+      <c r="AY20" s="58"/>
+      <c r="AZ20" s="58"/>
+      <c r="BA20" s="58"/>
+      <c r="BB20" s="58"/>
     </row>
     <row r="21" spans="1:54" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="62"/>
-      <c r="B21" s="62"/>
-      <c r="C21" s="62"/>
-      <c r="D21" s="62"/>
-      <c r="E21" s="62"/>
-      <c r="F21" s="62"/>
-      <c r="G21" s="62"/>
-      <c r="H21" s="62"/>
-      <c r="I21" s="62"/>
-      <c r="J21" s="62"/>
-      <c r="K21" s="62"/>
-      <c r="L21" s="62"/>
-      <c r="M21" s="62"/>
-      <c r="N21" s="62"/>
-      <c r="O21" s="62"/>
-      <c r="P21" s="62"/>
-      <c r="Q21" s="62"/>
-      <c r="R21" s="62"/>
-      <c r="S21" s="62"/>
-      <c r="T21" s="62"/>
-      <c r="U21" s="62"/>
-      <c r="V21" s="62"/>
-      <c r="W21" s="62"/>
-      <c r="X21" s="62"/>
-      <c r="Y21" s="62"/>
-      <c r="Z21" s="62"/>
-      <c r="AA21" s="62"/>
-      <c r="AB21" s="62"/>
-      <c r="AC21" s="62"/>
-      <c r="AD21" s="62"/>
-      <c r="AE21" s="62"/>
-      <c r="AF21" s="62"/>
-      <c r="AG21" s="62"/>
-      <c r="AH21" s="62"/>
-      <c r="AI21" s="62"/>
-      <c r="AJ21" s="62"/>
-      <c r="AK21" s="62"/>
-      <c r="AL21" s="62"/>
-      <c r="AM21" s="62"/>
-      <c r="AN21" s="62"/>
-      <c r="AO21" s="62"/>
-      <c r="AP21" s="62"/>
-      <c r="AQ21" s="62"/>
-      <c r="AR21" s="62"/>
-      <c r="AS21" s="62"/>
-      <c r="AT21" s="62"/>
-      <c r="AU21" s="62"/>
-      <c r="AV21" s="62"/>
-      <c r="AW21" s="62"/>
-      <c r="AX21" s="62"/>
-      <c r="AY21" s="62"/>
-      <c r="AZ21" s="62"/>
-      <c r="BA21" s="62"/>
-      <c r="BB21" s="62"/>
+      <c r="A21" s="58"/>
+      <c r="B21" s="58"/>
+      <c r="C21" s="58"/>
+      <c r="D21" s="58"/>
+      <c r="E21" s="58"/>
+      <c r="F21" s="58"/>
+      <c r="G21" s="58"/>
+      <c r="H21" s="58"/>
+      <c r="I21" s="58"/>
+      <c r="J21" s="58"/>
+      <c r="K21" s="58"/>
+      <c r="L21" s="58"/>
+      <c r="M21" s="58"/>
+      <c r="N21" s="58"/>
+      <c r="O21" s="58"/>
+      <c r="P21" s="58"/>
+      <c r="Q21" s="58"/>
+      <c r="R21" s="58"/>
+      <c r="S21" s="58"/>
+      <c r="T21" s="58"/>
+      <c r="U21" s="58"/>
+      <c r="V21" s="58"/>
+      <c r="W21" s="58"/>
+      <c r="X21" s="58"/>
+      <c r="Y21" s="58"/>
+      <c r="Z21" s="58"/>
+      <c r="AA21" s="58"/>
+      <c r="AB21" s="58"/>
+      <c r="AC21" s="58"/>
+      <c r="AD21" s="58"/>
+      <c r="AE21" s="58"/>
+      <c r="AF21" s="58"/>
+      <c r="AG21" s="58"/>
+      <c r="AH21" s="58"/>
+      <c r="AI21" s="58"/>
+      <c r="AJ21" s="58"/>
+      <c r="AK21" s="58"/>
+      <c r="AL21" s="58"/>
+      <c r="AM21" s="58"/>
+      <c r="AN21" s="58"/>
+      <c r="AO21" s="58"/>
+      <c r="AP21" s="58"/>
+      <c r="AQ21" s="58"/>
+      <c r="AR21" s="58"/>
+      <c r="AS21" s="58"/>
+      <c r="AT21" s="58"/>
+      <c r="AU21" s="58"/>
+      <c r="AV21" s="58"/>
+      <c r="AW21" s="58"/>
+      <c r="AX21" s="58"/>
+      <c r="AY21" s="58"/>
+      <c r="AZ21" s="58"/>
+      <c r="BA21" s="58"/>
+      <c r="BB21" s="58"/>
     </row>
     <row r="22" spans="1:54" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="62"/>
-      <c r="B22" s="62"/>
-      <c r="C22" s="62"/>
-      <c r="D22" s="62"/>
-      <c r="E22" s="62"/>
-      <c r="F22" s="62"/>
-      <c r="G22" s="62"/>
-      <c r="H22" s="62"/>
-      <c r="I22" s="62"/>
-      <c r="J22" s="62"/>
-      <c r="K22" s="62"/>
-      <c r="L22" s="62"/>
-      <c r="M22" s="62"/>
-      <c r="N22" s="62"/>
-      <c r="O22" s="62"/>
-      <c r="P22" s="62"/>
-      <c r="Q22" s="62"/>
-      <c r="R22" s="62"/>
-      <c r="S22" s="62"/>
-      <c r="T22" s="62"/>
-      <c r="U22" s="62"/>
-      <c r="V22" s="62"/>
-      <c r="W22" s="62"/>
-      <c r="X22" s="62"/>
-      <c r="Y22" s="62"/>
-      <c r="Z22" s="62"/>
-      <c r="AA22" s="62"/>
-      <c r="AB22" s="62"/>
-      <c r="AC22" s="62"/>
-      <c r="AD22" s="62"/>
-      <c r="AE22" s="62"/>
-      <c r="AF22" s="62"/>
-      <c r="AG22" s="62"/>
-      <c r="AH22" s="62"/>
-      <c r="AI22" s="62"/>
-      <c r="AJ22" s="62"/>
-      <c r="AK22" s="62"/>
-      <c r="AL22" s="62"/>
-      <c r="AM22" s="62"/>
-      <c r="AN22" s="62"/>
-      <c r="AO22" s="62"/>
-      <c r="AP22" s="62"/>
-      <c r="AQ22" s="62"/>
-      <c r="AR22" s="62"/>
-      <c r="AS22" s="62"/>
-      <c r="AT22" s="62"/>
-      <c r="AU22" s="62"/>
-      <c r="AV22" s="62"/>
-      <c r="AW22" s="62"/>
-      <c r="AX22" s="62"/>
-      <c r="AY22" s="62"/>
-      <c r="AZ22" s="62"/>
-      <c r="BA22" s="62"/>
-      <c r="BB22" s="62"/>
+      <c r="A22" s="58"/>
+      <c r="B22" s="58"/>
+      <c r="C22" s="58"/>
+      <c r="D22" s="58"/>
+      <c r="E22" s="58"/>
+      <c r="F22" s="58"/>
+      <c r="G22" s="58"/>
+      <c r="H22" s="58"/>
+      <c r="I22" s="58"/>
+      <c r="J22" s="58"/>
+      <c r="K22" s="58"/>
+      <c r="L22" s="58"/>
+      <c r="M22" s="58"/>
+      <c r="N22" s="58"/>
+      <c r="O22" s="58"/>
+      <c r="P22" s="58"/>
+      <c r="Q22" s="58"/>
+      <c r="R22" s="58"/>
+      <c r="S22" s="58"/>
+      <c r="T22" s="58"/>
+      <c r="U22" s="58"/>
+      <c r="V22" s="58"/>
+      <c r="W22" s="58"/>
+      <c r="X22" s="58"/>
+      <c r="Y22" s="58"/>
+      <c r="Z22" s="58"/>
+      <c r="AA22" s="58"/>
+      <c r="AB22" s="58"/>
+      <c r="AC22" s="58"/>
+      <c r="AD22" s="58"/>
+      <c r="AE22" s="58"/>
+      <c r="AF22" s="58"/>
+      <c r="AG22" s="58"/>
+      <c r="AH22" s="58"/>
+      <c r="AI22" s="58"/>
+      <c r="AJ22" s="58"/>
+      <c r="AK22" s="58"/>
+      <c r="AL22" s="58"/>
+      <c r="AM22" s="58"/>
+      <c r="AN22" s="58"/>
+      <c r="AO22" s="58"/>
+      <c r="AP22" s="58"/>
+      <c r="AQ22" s="58"/>
+      <c r="AR22" s="58"/>
+      <c r="AS22" s="58"/>
+      <c r="AT22" s="58"/>
+      <c r="AU22" s="58"/>
+      <c r="AV22" s="58"/>
+      <c r="AW22" s="58"/>
+      <c r="AX22" s="58"/>
+      <c r="AY22" s="58"/>
+      <c r="AZ22" s="58"/>
+      <c r="BA22" s="58"/>
+      <c r="BB22" s="58"/>
     </row>
     <row r="23" spans="1:54" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="62"/>
-      <c r="B23" s="62"/>
-      <c r="C23" s="62"/>
-      <c r="D23" s="62"/>
-      <c r="E23" s="62"/>
-      <c r="F23" s="62"/>
-      <c r="G23" s="62"/>
-      <c r="H23" s="62"/>
-      <c r="I23" s="62"/>
-      <c r="J23" s="62"/>
-      <c r="K23" s="62"/>
-      <c r="L23" s="62"/>
-      <c r="M23" s="62"/>
-      <c r="N23" s="62"/>
-      <c r="O23" s="62"/>
-      <c r="P23" s="62"/>
-      <c r="Q23" s="62"/>
-      <c r="R23" s="62"/>
-      <c r="S23" s="62"/>
-      <c r="T23" s="62"/>
-      <c r="U23" s="62"/>
-      <c r="V23" s="62"/>
-      <c r="W23" s="62"/>
-      <c r="X23" s="62"/>
-      <c r="Y23" s="62"/>
-      <c r="Z23" s="62"/>
-      <c r="AA23" s="62"/>
-      <c r="AB23" s="62"/>
-      <c r="AC23" s="62"/>
-      <c r="AD23" s="62"/>
-      <c r="AE23" s="62"/>
-      <c r="AF23" s="62"/>
-      <c r="AG23" s="62"/>
-      <c r="AH23" s="62"/>
-      <c r="AI23" s="62"/>
-      <c r="AJ23" s="62"/>
-      <c r="AK23" s="62"/>
-      <c r="AL23" s="62"/>
-      <c r="AM23" s="62"/>
-      <c r="AN23" s="62"/>
-      <c r="AO23" s="62"/>
-      <c r="AP23" s="62"/>
-      <c r="AQ23" s="62"/>
-      <c r="AR23" s="62"/>
-      <c r="AS23" s="62"/>
-      <c r="AT23" s="62"/>
-      <c r="AU23" s="62"/>
-      <c r="AV23" s="62"/>
-      <c r="AW23" s="62"/>
-      <c r="AX23" s="62"/>
-      <c r="AY23" s="62"/>
-      <c r="AZ23" s="62"/>
-      <c r="BA23" s="62"/>
-      <c r="BB23" s="62"/>
+      <c r="A23" s="58"/>
+      <c r="B23" s="58"/>
+      <c r="C23" s="58"/>
+      <c r="D23" s="58"/>
+      <c r="E23" s="58"/>
+      <c r="F23" s="58"/>
+      <c r="G23" s="58"/>
+      <c r="H23" s="58"/>
+      <c r="I23" s="58"/>
+      <c r="J23" s="58"/>
+      <c r="K23" s="58"/>
+      <c r="L23" s="58"/>
+      <c r="M23" s="58"/>
+      <c r="N23" s="58"/>
+      <c r="O23" s="58"/>
+      <c r="P23" s="58"/>
+      <c r="Q23" s="58"/>
+      <c r="R23" s="58"/>
+      <c r="S23" s="58"/>
+      <c r="T23" s="58"/>
+      <c r="U23" s="58"/>
+      <c r="V23" s="58"/>
+      <c r="W23" s="58"/>
+      <c r="X23" s="58"/>
+      <c r="Y23" s="58"/>
+      <c r="Z23" s="58"/>
+      <c r="AA23" s="58"/>
+      <c r="AB23" s="58"/>
+      <c r="AC23" s="58"/>
+      <c r="AD23" s="58"/>
+      <c r="AE23" s="58"/>
+      <c r="AF23" s="58"/>
+      <c r="AG23" s="58"/>
+      <c r="AH23" s="58"/>
+      <c r="AI23" s="58"/>
+      <c r="AJ23" s="58"/>
+      <c r="AK23" s="58"/>
+      <c r="AL23" s="58"/>
+      <c r="AM23" s="58"/>
+      <c r="AN23" s="58"/>
+      <c r="AO23" s="58"/>
+      <c r="AP23" s="58"/>
+      <c r="AQ23" s="58"/>
+      <c r="AR23" s="58"/>
+      <c r="AS23" s="58"/>
+      <c r="AT23" s="58"/>
+      <c r="AU23" s="58"/>
+      <c r="AV23" s="58"/>
+      <c r="AW23" s="58"/>
+      <c r="AX23" s="58"/>
+      <c r="AY23" s="58"/>
+      <c r="AZ23" s="58"/>
+      <c r="BA23" s="58"/>
+      <c r="BB23" s="58"/>
     </row>
     <row r="24" spans="1:54" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="62"/>
-      <c r="B24" s="62"/>
-      <c r="C24" s="62"/>
-      <c r="D24" s="62"/>
-      <c r="E24" s="62"/>
-      <c r="F24" s="62"/>
-      <c r="G24" s="62"/>
-      <c r="H24" s="62"/>
-      <c r="I24" s="62"/>
-      <c r="J24" s="62"/>
-      <c r="K24" s="62"/>
-      <c r="L24" s="62"/>
-      <c r="M24" s="62"/>
-      <c r="N24" s="62"/>
-      <c r="O24" s="62"/>
-      <c r="P24" s="62"/>
-      <c r="Q24" s="62"/>
-      <c r="R24" s="62"/>
-      <c r="S24" s="62"/>
-      <c r="T24" s="62"/>
-      <c r="U24" s="62"/>
-      <c r="V24" s="62"/>
-      <c r="W24" s="62"/>
-      <c r="X24" s="62"/>
-      <c r="Y24" s="62"/>
-      <c r="Z24" s="62"/>
-      <c r="AA24" s="62"/>
-      <c r="AB24" s="62"/>
-      <c r="AC24" s="62"/>
-      <c r="AD24" s="62"/>
-      <c r="AE24" s="62"/>
-      <c r="AF24" s="62"/>
-      <c r="AG24" s="62"/>
-      <c r="AH24" s="62"/>
-      <c r="AI24" s="62"/>
-      <c r="AJ24" s="62"/>
-      <c r="AK24" s="62"/>
-      <c r="AL24" s="62"/>
-      <c r="AM24" s="62"/>
-      <c r="AN24" s="62"/>
-      <c r="AO24" s="62"/>
-      <c r="AP24" s="62"/>
-      <c r="AQ24" s="62"/>
-      <c r="AR24" s="62"/>
-      <c r="AS24" s="62"/>
-      <c r="AT24" s="62"/>
-      <c r="AU24" s="62"/>
-      <c r="AV24" s="62"/>
-      <c r="AW24" s="62"/>
-      <c r="AX24" s="62"/>
-      <c r="AY24" s="62"/>
-      <c r="AZ24" s="62"/>
-      <c r="BA24" s="62"/>
-      <c r="BB24" s="62"/>
+      <c r="A24" s="58"/>
+      <c r="B24" s="58"/>
+      <c r="C24" s="58"/>
+      <c r="D24" s="58"/>
+      <c r="E24" s="58"/>
+      <c r="F24" s="58"/>
+      <c r="G24" s="58"/>
+      <c r="H24" s="58"/>
+      <c r="I24" s="58"/>
+      <c r="J24" s="58"/>
+      <c r="K24" s="58"/>
+      <c r="L24" s="58"/>
+      <c r="M24" s="58"/>
+      <c r="N24" s="58"/>
+      <c r="O24" s="58"/>
+      <c r="P24" s="58"/>
+      <c r="Q24" s="58"/>
+      <c r="R24" s="58"/>
+      <c r="S24" s="58"/>
+      <c r="T24" s="58"/>
+      <c r="U24" s="58"/>
+      <c r="V24" s="58"/>
+      <c r="W24" s="58"/>
+      <c r="X24" s="58"/>
+      <c r="Y24" s="58"/>
+      <c r="Z24" s="58"/>
+      <c r="AA24" s="58"/>
+      <c r="AB24" s="58"/>
+      <c r="AC24" s="58"/>
+      <c r="AD24" s="58"/>
+      <c r="AE24" s="58"/>
+      <c r="AF24" s="58"/>
+      <c r="AG24" s="58"/>
+      <c r="AH24" s="58"/>
+      <c r="AI24" s="58"/>
+      <c r="AJ24" s="58"/>
+      <c r="AK24" s="58"/>
+      <c r="AL24" s="58"/>
+      <c r="AM24" s="58"/>
+      <c r="AN24" s="58"/>
+      <c r="AO24" s="58"/>
+      <c r="AP24" s="58"/>
+      <c r="AQ24" s="58"/>
+      <c r="AR24" s="58"/>
+      <c r="AS24" s="58"/>
+      <c r="AT24" s="58"/>
+      <c r="AU24" s="58"/>
+      <c r="AV24" s="58"/>
+      <c r="AW24" s="58"/>
+      <c r="AX24" s="58"/>
+      <c r="AY24" s="58"/>
+      <c r="AZ24" s="58"/>
+      <c r="BA24" s="58"/>
+      <c r="BB24" s="58"/>
     </row>
     <row r="25" spans="1:54" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="62"/>
-      <c r="B25" s="62"/>
-      <c r="C25" s="62"/>
-      <c r="D25" s="62"/>
-      <c r="E25" s="62"/>
-      <c r="F25" s="62"/>
-      <c r="G25" s="62"/>
-      <c r="H25" s="62"/>
-      <c r="I25" s="62"/>
-      <c r="J25" s="62"/>
-      <c r="K25" s="62"/>
-      <c r="L25" s="62"/>
-      <c r="M25" s="62"/>
-      <c r="N25" s="62"/>
-      <c r="O25" s="62"/>
-      <c r="P25" s="62"/>
-      <c r="Q25" s="62"/>
-      <c r="R25" s="62"/>
-      <c r="S25" s="62"/>
-      <c r="T25" s="62"/>
-      <c r="U25" s="62"/>
-      <c r="V25" s="62"/>
-      <c r="W25" s="62"/>
-      <c r="X25" s="62"/>
-      <c r="Y25" s="62"/>
-      <c r="Z25" s="62"/>
-      <c r="AA25" s="62"/>
-      <c r="AB25" s="62"/>
-      <c r="AC25" s="62"/>
-      <c r="AD25" s="62"/>
-      <c r="AE25" s="62"/>
-      <c r="AF25" s="62"/>
-      <c r="AG25" s="62"/>
-      <c r="AH25" s="62"/>
-      <c r="AI25" s="62"/>
-      <c r="AJ25" s="62"/>
-      <c r="AK25" s="62"/>
-      <c r="AL25" s="62"/>
-      <c r="AM25" s="62"/>
-      <c r="AN25" s="62"/>
-      <c r="AO25" s="62"/>
-      <c r="AP25" s="62"/>
-      <c r="AQ25" s="62"/>
-      <c r="AR25" s="62"/>
-      <c r="AS25" s="62"/>
-      <c r="AT25" s="62"/>
-      <c r="AU25" s="62"/>
-      <c r="AV25" s="62"/>
-      <c r="AW25" s="62"/>
-      <c r="AX25" s="62"/>
-      <c r="AY25" s="62"/>
-      <c r="AZ25" s="62"/>
-      <c r="BA25" s="62"/>
-      <c r="BB25" s="62"/>
+      <c r="A25" s="58"/>
+      <c r="B25" s="58"/>
+      <c r="C25" s="58"/>
+      <c r="D25" s="58"/>
+      <c r="E25" s="58"/>
+      <c r="F25" s="58"/>
+      <c r="G25" s="58"/>
+      <c r="H25" s="58"/>
+      <c r="I25" s="58"/>
+      <c r="J25" s="58"/>
+      <c r="K25" s="58"/>
+      <c r="L25" s="58"/>
+      <c r="M25" s="58"/>
+      <c r="N25" s="58"/>
+      <c r="O25" s="58"/>
+      <c r="P25" s="58"/>
+      <c r="Q25" s="58"/>
+      <c r="R25" s="58"/>
+      <c r="S25" s="58"/>
+      <c r="T25" s="58"/>
+      <c r="U25" s="58"/>
+      <c r="V25" s="58"/>
+      <c r="W25" s="58"/>
+      <c r="X25" s="58"/>
+      <c r="Y25" s="58"/>
+      <c r="Z25" s="58"/>
+      <c r="AA25" s="58"/>
+      <c r="AB25" s="58"/>
+      <c r="AC25" s="58"/>
+      <c r="AD25" s="58"/>
+      <c r="AE25" s="58"/>
+      <c r="AF25" s="58"/>
+      <c r="AG25" s="58"/>
+      <c r="AH25" s="58"/>
+      <c r="AI25" s="58"/>
+      <c r="AJ25" s="58"/>
+      <c r="AK25" s="58"/>
+      <c r="AL25" s="58"/>
+      <c r="AM25" s="58"/>
+      <c r="AN25" s="58"/>
+      <c r="AO25" s="58"/>
+      <c r="AP25" s="58"/>
+      <c r="AQ25" s="58"/>
+      <c r="AR25" s="58"/>
+      <c r="AS25" s="58"/>
+      <c r="AT25" s="58"/>
+      <c r="AU25" s="58"/>
+      <c r="AV25" s="58"/>
+      <c r="AW25" s="58"/>
+      <c r="AX25" s="58"/>
+      <c r="AY25" s="58"/>
+      <c r="AZ25" s="58"/>
+      <c r="BA25" s="58"/>
+      <c r="BB25" s="58"/>
     </row>
     <row r="26" spans="1:54" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="62"/>
-      <c r="B26" s="62"/>
-      <c r="C26" s="62"/>
-      <c r="D26" s="62"/>
-      <c r="E26" s="62"/>
-      <c r="F26" s="62"/>
-      <c r="G26" s="62"/>
-      <c r="H26" s="62"/>
-      <c r="I26" s="62"/>
-      <c r="J26" s="62"/>
-      <c r="K26" s="62"/>
-      <c r="L26" s="62"/>
-      <c r="M26" s="62"/>
-      <c r="N26" s="62"/>
-      <c r="O26" s="62"/>
-      <c r="P26" s="62"/>
-      <c r="Q26" s="62"/>
-      <c r="R26" s="62"/>
-      <c r="S26" s="62"/>
-      <c r="T26" s="62"/>
-      <c r="U26" s="62"/>
-      <c r="V26" s="62"/>
-      <c r="W26" s="62"/>
-      <c r="X26" s="62"/>
-      <c r="Y26" s="62"/>
-      <c r="Z26" s="62"/>
-      <c r="AA26" s="62"/>
-      <c r="AB26" s="62"/>
-      <c r="AC26" s="62"/>
-      <c r="AD26" s="62"/>
-      <c r="AE26" s="62"/>
-      <c r="AF26" s="62"/>
-      <c r="AG26" s="62"/>
-      <c r="AH26" s="62"/>
-      <c r="AI26" s="62"/>
-      <c r="AJ26" s="62"/>
-      <c r="AK26" s="62"/>
-      <c r="AL26" s="62"/>
-      <c r="AM26" s="62"/>
-      <c r="AN26" s="62"/>
-      <c r="AO26" s="62"/>
-      <c r="AP26" s="62"/>
-      <c r="AQ26" s="62"/>
-      <c r="AR26" s="62"/>
-      <c r="AS26" s="62"/>
-      <c r="AT26" s="62"/>
-      <c r="AU26" s="62"/>
-      <c r="AV26" s="62"/>
-      <c r="AW26" s="62"/>
-      <c r="AX26" s="62"/>
-      <c r="AY26" s="62"/>
-      <c r="AZ26" s="62"/>
-      <c r="BA26" s="62"/>
-      <c r="BB26" s="62"/>
+      <c r="A26" s="58"/>
+      <c r="B26" s="58"/>
+      <c r="C26" s="58"/>
+      <c r="D26" s="58"/>
+      <c r="E26" s="58"/>
+      <c r="F26" s="58"/>
+      <c r="G26" s="58"/>
+      <c r="H26" s="58"/>
+      <c r="I26" s="58"/>
+      <c r="J26" s="58"/>
+      <c r="K26" s="58"/>
+      <c r="L26" s="58"/>
+      <c r="M26" s="58"/>
+      <c r="N26" s="58"/>
+      <c r="O26" s="58"/>
+      <c r="P26" s="58"/>
+      <c r="Q26" s="58"/>
+      <c r="R26" s="58"/>
+      <c r="S26" s="58"/>
+      <c r="T26" s="58"/>
+      <c r="U26" s="58"/>
+      <c r="V26" s="58"/>
+      <c r="W26" s="58"/>
+      <c r="X26" s="58"/>
+      <c r="Y26" s="58"/>
+      <c r="Z26" s="58"/>
+      <c r="AA26" s="58"/>
+      <c r="AB26" s="58"/>
+      <c r="AC26" s="58"/>
+      <c r="AD26" s="58"/>
+      <c r="AE26" s="58"/>
+      <c r="AF26" s="58"/>
+      <c r="AG26" s="58"/>
+      <c r="AH26" s="58"/>
+      <c r="AI26" s="58"/>
+      <c r="AJ26" s="58"/>
+      <c r="AK26" s="58"/>
+      <c r="AL26" s="58"/>
+      <c r="AM26" s="58"/>
+      <c r="AN26" s="58"/>
+      <c r="AO26" s="58"/>
+      <c r="AP26" s="58"/>
+      <c r="AQ26" s="58"/>
+      <c r="AR26" s="58"/>
+      <c r="AS26" s="58"/>
+      <c r="AT26" s="58"/>
+      <c r="AU26" s="58"/>
+      <c r="AV26" s="58"/>
+      <c r="AW26" s="58"/>
+      <c r="AX26" s="58"/>
+      <c r="AY26" s="58"/>
+      <c r="AZ26" s="58"/>
+      <c r="BA26" s="58"/>
+      <c r="BB26" s="58"/>
     </row>
     <row r="27" spans="1:54" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="62"/>
-      <c r="B27" s="62"/>
-      <c r="C27" s="62"/>
-      <c r="D27" s="62"/>
-      <c r="E27" s="62"/>
-      <c r="F27" s="62"/>
-      <c r="G27" s="62"/>
-      <c r="H27" s="62"/>
-      <c r="I27" s="62"/>
-      <c r="J27" s="62"/>
-      <c r="K27" s="62"/>
-      <c r="L27" s="62"/>
-      <c r="M27" s="62"/>
-      <c r="N27" s="62"/>
-      <c r="O27" s="62"/>
-      <c r="P27" s="62"/>
-      <c r="Q27" s="62"/>
-      <c r="R27" s="62"/>
-      <c r="S27" s="62"/>
-      <c r="T27" s="62"/>
-      <c r="U27" s="62"/>
-      <c r="V27" s="62"/>
-      <c r="W27" s="62"/>
-      <c r="X27" s="62"/>
-      <c r="Y27" s="62"/>
-      <c r="Z27" s="62"/>
-      <c r="AA27" s="62"/>
-      <c r="AB27" s="62"/>
-      <c r="AC27" s="62"/>
-      <c r="AD27" s="62"/>
-      <c r="AE27" s="62"/>
-      <c r="AF27" s="62"/>
-      <c r="AG27" s="62"/>
-      <c r="AH27" s="62"/>
-      <c r="AI27" s="62"/>
-      <c r="AJ27" s="62"/>
-      <c r="AK27" s="62"/>
-      <c r="AL27" s="62"/>
-      <c r="AM27" s="62"/>
-      <c r="AN27" s="62"/>
-      <c r="AO27" s="62"/>
-      <c r="AP27" s="62"/>
-      <c r="AQ27" s="62"/>
-      <c r="AR27" s="62"/>
-      <c r="AS27" s="62"/>
-      <c r="AT27" s="62"/>
-      <c r="AU27" s="62"/>
-      <c r="AV27" s="62"/>
-      <c r="AW27" s="62"/>
-      <c r="AX27" s="62"/>
-      <c r="AY27" s="62"/>
-      <c r="AZ27" s="62"/>
-      <c r="BA27" s="62"/>
-      <c r="BB27" s="62"/>
+      <c r="A27" s="58"/>
+      <c r="B27" s="58"/>
+      <c r="C27" s="58"/>
+      <c r="D27" s="58"/>
+      <c r="E27" s="58"/>
+      <c r="F27" s="58"/>
+      <c r="G27" s="58"/>
+      <c r="H27" s="58"/>
+      <c r="I27" s="58"/>
+      <c r="J27" s="58"/>
+      <c r="K27" s="58"/>
+      <c r="L27" s="58"/>
+      <c r="M27" s="58"/>
+      <c r="N27" s="58"/>
+      <c r="O27" s="58"/>
+      <c r="P27" s="58"/>
+      <c r="Q27" s="58"/>
+      <c r="R27" s="58"/>
+      <c r="S27" s="58"/>
+      <c r="T27" s="58"/>
+      <c r="U27" s="58"/>
+      <c r="V27" s="58"/>
+      <c r="W27" s="58"/>
+      <c r="X27" s="58"/>
+      <c r="Y27" s="58"/>
+      <c r="Z27" s="58"/>
+      <c r="AA27" s="58"/>
+      <c r="AB27" s="58"/>
+      <c r="AC27" s="58"/>
+      <c r="AD27" s="58"/>
+      <c r="AE27" s="58"/>
+      <c r="AF27" s="58"/>
+      <c r="AG27" s="58"/>
+      <c r="AH27" s="58"/>
+      <c r="AI27" s="58"/>
+      <c r="AJ27" s="58"/>
+      <c r="AK27" s="58"/>
+      <c r="AL27" s="58"/>
+      <c r="AM27" s="58"/>
+      <c r="AN27" s="58"/>
+      <c r="AO27" s="58"/>
+      <c r="AP27" s="58"/>
+      <c r="AQ27" s="58"/>
+      <c r="AR27" s="58"/>
+      <c r="AS27" s="58"/>
+      <c r="AT27" s="58"/>
+      <c r="AU27" s="58"/>
+      <c r="AV27" s="58"/>
+      <c r="AW27" s="58"/>
+      <c r="AX27" s="58"/>
+      <c r="AY27" s="58"/>
+      <c r="AZ27" s="58"/>
+      <c r="BA27" s="58"/>
+      <c r="BB27" s="58"/>
     </row>
     <row r="28" spans="1:54" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="62"/>
-      <c r="B28" s="62"/>
-      <c r="C28" s="62"/>
-      <c r="D28" s="62"/>
-      <c r="E28" s="62"/>
-      <c r="F28" s="62"/>
-      <c r="G28" s="62"/>
-      <c r="H28" s="62"/>
-      <c r="I28" s="62"/>
-      <c r="J28" s="62"/>
-      <c r="K28" s="62"/>
-      <c r="L28" s="62"/>
-      <c r="M28" s="62"/>
-      <c r="N28" s="62"/>
-      <c r="O28" s="62"/>
-      <c r="P28" s="62"/>
-      <c r="Q28" s="62"/>
-      <c r="R28" s="62"/>
-      <c r="S28" s="62"/>
-      <c r="T28" s="62"/>
-      <c r="U28" s="62"/>
-      <c r="V28" s="62"/>
-      <c r="W28" s="62"/>
-      <c r="X28" s="62"/>
-      <c r="Y28" s="62"/>
-      <c r="Z28" s="62"/>
-      <c r="AA28" s="62"/>
-      <c r="AB28" s="62"/>
-      <c r="AC28" s="62"/>
-      <c r="AD28" s="62"/>
-      <c r="AE28" s="62"/>
-      <c r="AF28" s="62"/>
-      <c r="AG28" s="62"/>
-      <c r="AH28" s="62"/>
-      <c r="AI28" s="62"/>
-      <c r="AJ28" s="62"/>
-      <c r="AK28" s="62"/>
-      <c r="AL28" s="62"/>
-      <c r="AM28" s="62"/>
-      <c r="AN28" s="62"/>
-      <c r="AO28" s="62"/>
-      <c r="AP28" s="62"/>
-      <c r="AQ28" s="62"/>
-      <c r="AR28" s="62"/>
-      <c r="AS28" s="62"/>
-      <c r="AT28" s="62"/>
-      <c r="AU28" s="62"/>
-      <c r="AV28" s="62"/>
-      <c r="AW28" s="62"/>
-      <c r="AX28" s="62"/>
-      <c r="AY28" s="62"/>
-      <c r="AZ28" s="62"/>
-      <c r="BA28" s="62"/>
-      <c r="BB28" s="62"/>
+      <c r="A28" s="58"/>
+      <c r="B28" s="58"/>
+      <c r="C28" s="58"/>
+      <c r="D28" s="58"/>
+      <c r="E28" s="58"/>
+      <c r="F28" s="58"/>
+      <c r="G28" s="58"/>
+      <c r="H28" s="58"/>
+      <c r="I28" s="58"/>
+      <c r="J28" s="58"/>
+      <c r="K28" s="58"/>
+      <c r="L28" s="58"/>
+      <c r="M28" s="58"/>
+      <c r="N28" s="58"/>
+      <c r="O28" s="58"/>
+      <c r="P28" s="58"/>
+      <c r="Q28" s="58"/>
+      <c r="R28" s="58"/>
+      <c r="S28" s="58"/>
+      <c r="T28" s="58"/>
+      <c r="U28" s="58"/>
+      <c r="V28" s="58"/>
+      <c r="W28" s="58"/>
+      <c r="X28" s="58"/>
+      <c r="Y28" s="58"/>
+      <c r="Z28" s="58"/>
+      <c r="AA28" s="58"/>
+      <c r="AB28" s="58"/>
+      <c r="AC28" s="58"/>
+      <c r="AD28" s="58"/>
+      <c r="AE28" s="58"/>
+      <c r="AF28" s="58"/>
+      <c r="AG28" s="58"/>
+      <c r="AH28" s="58"/>
+      <c r="AI28" s="58"/>
+      <c r="AJ28" s="58"/>
+      <c r="AK28" s="58"/>
+      <c r="AL28" s="58"/>
+      <c r="AM28" s="58"/>
+      <c r="AN28" s="58"/>
+      <c r="AO28" s="58"/>
+      <c r="AP28" s="58"/>
+      <c r="AQ28" s="58"/>
+      <c r="AR28" s="58"/>
+      <c r="AS28" s="58"/>
+      <c r="AT28" s="58"/>
+      <c r="AU28" s="58"/>
+      <c r="AV28" s="58"/>
+      <c r="AW28" s="58"/>
+      <c r="AX28" s="58"/>
+      <c r="AY28" s="58"/>
+      <c r="AZ28" s="58"/>
+      <c r="BA28" s="58"/>
+      <c r="BB28" s="58"/>
     </row>
   </sheetData>
   <mergeCells count="14">
